--- a/spl.xlsx
+++ b/spl.xlsx
@@ -6,7 +6,9 @@
     <sheet state="visible" name="Form Responses 1" sheetId="1" r:id="rId5"/>
     <sheet state="visible" name="Sheet1" sheetId="2" r:id="rId6"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'Form Responses 1'!$A$1:$Q$99</definedName>
+  </definedNames>
   <calcPr/>
 </workbook>
 </file>
@@ -17,7 +19,7 @@
     <author/>
   </authors>
   <commentList>
-    <comment authorId="0" ref="N22">
+    <comment authorId="0" ref="N21">
       <text>
         <t xml:space="preserve">Responder updated this value.</t>
       </text>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="963" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="501">
   <si>
     <t>Timestamp</t>
   </si>
@@ -169,7 +171,7 @@
     <t xml:space="preserve">AVISH </t>
   </si>
   <si>
-    <t>https://drive.google.com/open?id=1bWKdsZBR-Xt1zmRSGSIBiTgwtstUJN7Y</t>
+    <t>https://drive.google.com/file/d/1nvO7O3TZspXCHUk5Wu0hImS_yeGrykNv/view?usp=drive_link</t>
   </si>
   <si>
     <t>https://drive.google.com/open?id=1duo3RXZvzmN9HLKZgBkiW73L995XNtJX</t>
@@ -262,25 +264,13 @@
     <t>T2603202235330641227775</t>
   </si>
   <si>
-    <t xml:space="preserve">Nityanand Kolambkar </t>
-  </si>
-  <si>
-    <t>Nitu K</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/open?id=1m5xcDGJ2ZvOxB4PIlZlttyc1NXX_dCgp</t>
-  </si>
-  <si>
-    <t>https://drive.google.com/open?id=1mRHADu8OOWF613juSEDRbqG7X4ezffgZ</t>
-  </si>
-  <si>
     <t>Vikram naik</t>
   </si>
   <si>
     <t>VIKRAM</t>
   </si>
   <si>
-    <t>https://drive.google.com/open?id=17DSJxn9-yqNxjVpBqTPbLSTL1diCc8Oe</t>
+    <t>https://drive.google.com/file/d/1KbkNAbQVFkGvOQw0F0NaeIFKrhvkMeX-/view?usp=drive_link</t>
   </si>
   <si>
     <t>https://drive.google.com/open?id=1L11KOOm90JnX3-hdDFjUPRfpre9ITlC6</t>
@@ -481,7 +471,7 @@
     <t>03</t>
   </si>
   <si>
-    <t>https://drive.google.com/open?id=17TQvSncMx7OdBY_VgmF_yiGhbNhJCNaH</t>
+    <t>https://drive.google.com/file/d/1f7nbHmF74d8yZVkmv56_xjAKw6v2e8gL/view?usp=drive_link</t>
   </si>
   <si>
     <t>https://drive.google.com/open?id=1L4P9nZSjAKql6q5E-zTFZlAOYh8KvRQD</t>
@@ -601,7 +591,7 @@
     <t xml:space="preserve">Akash Kolambkar </t>
   </si>
   <si>
-    <t>AKASH</t>
+    <t>ma</t>
   </si>
   <si>
     <t>https://drive.google.com/open?id=1NNH9riRIa46-Ty2l7C7cUwechQ1KOwM6</t>
@@ -1018,7 +1008,7 @@
     <t>ALAN</t>
   </si>
   <si>
-    <t>https://drive.google.com/open?id=16E31KSYyK83ydJMRNQNb_WngfGOkEAPi</t>
+    <t>https://drive.google.com/file/d/1dAP_tGc96KMd3-6sE4ju66uPAZrb2hdg/view?usp=drive_link</t>
   </si>
   <si>
     <t>https://drive.google.com/open?id=13dc9J_izKK5MOdrwl9tvPe6qUKOoBjFY</t>
@@ -1276,7 +1266,7 @@
     <t>Sanmay</t>
   </si>
   <si>
-    <t>https://drive.google.com/open?id=1Bpxc2-jTJ27P4Y_rN14AqjLTYaHTVz3A</t>
+    <t>https://drive.google.com/file/d/1AZd0Z-pSkR6DLUMu3gExw6TXJfuN08M-/view?usp=drive_link</t>
   </si>
   <si>
     <t>https://drive.google.com/open?id=1xCJHzjJ1k_JcGj3FtDLrvJoF-Bsea2Qq</t>
@@ -1433,6 +1423,117 @@
   </si>
   <si>
     <t>T2603251454264661668879</t>
+  </si>
+  <si>
+    <t>Nityanand Kolambkar</t>
+  </si>
+  <si>
+    <t>Nitu.K</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1PP4ItR6jhaFq4zSN83roxO454mVpf5kW</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1L8tlIIAf4EyK-LHlE6Zm9UIQVJOzMnQI</t>
+  </si>
+  <si>
+    <t>Nitu</t>
+  </si>
+  <si>
+    <t>Santosh Kolambkar</t>
+  </si>
+  <si>
+    <t>Santosh</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1mXsox0vojtpArgOyrI-Td5RmHUWNvr7n</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1lKZ2f_2E0KvZLXQT-9BV_FmQgab_IUEW</t>
+  </si>
+  <si>
+    <t>T2603301637442477578689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abhishek Gurav </t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1PaVUEyoM5wTukLTdmGda1IRDtb21FHRW</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1PMhq5NgxZHWzwx27AcL7DGn-KE9dCxa8</t>
+  </si>
+  <si>
+    <t>T2603301646415446960809</t>
+  </si>
+  <si>
+    <t>Kaushik Salaskar</t>
+  </si>
+  <si>
+    <t>Kaushik</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1I9D3TwDLynwLqWpPQ3S3H7hyg28ACZBw</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1YmLJMFFXW4hekML72zACvzpLcNAQSaYM</t>
+  </si>
+  <si>
+    <t>T2603302003300038694215</t>
+  </si>
+  <si>
+    <t>Vikas Gurav</t>
+  </si>
+  <si>
+    <t>Vikas</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1g0lZ-HU5iNZSI2ZeW1asN6X2U9ACSIGA</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1J85oNTnzY9DxJN1REcvi7pGn3iWfr1U0</t>
+  </si>
+  <si>
+    <t>T2603302034010211795546</t>
+  </si>
+  <si>
+    <t>Manoj gouda</t>
+  </si>
+  <si>
+    <t>Manoj</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1QeHOeYVY6X_WXrhIGGKOb4ed4KAE2bRf</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1Z8kLyixO87t7QFlUA1FxE_rOSgORvK6t</t>
+  </si>
+  <si>
+    <t>T2603302047340348898518</t>
+  </si>
+  <si>
+    <t>Manjunath Gouda</t>
+  </si>
+  <si>
+    <t>Manju GL</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1rGyyF1-4OTUlOAFUUVbfAiQz3xWi4f3_</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1VW3SR7vU83Cjo5LEUX8Ovp4GJ-nkVamf</t>
+  </si>
+  <si>
+    <t>Vivek Rane</t>
+  </si>
+  <si>
+    <t>Vivek</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1tz8J5R3u_Te2A_nPJFgp7Kvv0sIOKEyL</t>
+  </si>
+  <si>
+    <t>https://drive.google.com/open?id=1gjHj1wXZ9SRwxKodD7bR3Sz3FM6H2AcZ</t>
   </si>
 </sst>
 </file>
@@ -1580,10 +1681,10 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf quotePrefix="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf quotePrefix="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -1673,7 +1774,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:Q92" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:Q99" displayName="Form_Responses" name="Form_Responses" id="1">
+  <autoFilter ref="$A$1:$Q$99"/>
   <tableColumns count="17">
     <tableColumn name="Timestamp" id="1"/>
     <tableColumn name="Full Name" id="2"/>
@@ -1965,7 +2067,7 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="6">
-        <v>46101.01463547454</v>
+        <v>46101.02407407408</v>
       </c>
       <c r="B2" s="7" t="s">
         <v>17</v>
@@ -2460,16 +2562,16 @@
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="15">
-        <v>46101.980599560186</v>
+        <v>46102.38793730324</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>77</v>
       </c>
       <c r="C11" s="16">
-        <v>26.0</v>
+        <v>25.0</v>
       </c>
       <c r="D11" s="16">
-        <v>6.360009769E9</v>
+        <v>9.448837129E9</v>
       </c>
       <c r="E11" s="16" t="s">
         <v>18</v>
@@ -2487,7 +2589,7 @@
         <v>78</v>
       </c>
       <c r="J11" s="16">
-        <v>45.0</v>
+        <v>21.0</v>
       </c>
       <c r="K11" s="16" t="s">
         <v>23</v>
@@ -2498,13 +2600,15 @@
       <c r="M11" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="N11" s="18"/>
+      <c r="N11" s="16" t="s">
+        <v>81</v>
+      </c>
       <c r="O11" s="18"/>
       <c r="P11" s="13" t="s">
         <v>27</v>
       </c>
       <c r="Q11" s="14">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="R11" s="5"/>
       <c r="S11" s="5"/>
@@ -2513,22 +2617,22 @@
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="15">
-        <v>46102.38793730324</v>
+        <v>46102.424570856485</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C12" s="16">
-        <v>25.0</v>
+        <v>24.0</v>
       </c>
       <c r="D12" s="16">
-        <v>9.448837129E9</v>
+        <v>9.480500716E9</v>
       </c>
       <c r="E12" s="16" t="s">
-        <v>18</v>
+        <v>83</v>
       </c>
       <c r="F12" s="16" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="G12" s="16" t="s">
         <v>20</v>
@@ -2537,29 +2641,29 @@
         <v>37</v>
       </c>
       <c r="I12" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="J12" s="16">
-        <v>21.0</v>
+        <v>85</v>
+      </c>
+      <c r="J12" s="19" t="s">
+        <v>86</v>
       </c>
       <c r="K12" s="16" t="s">
         <v>23</v>
       </c>
       <c r="L12" s="17" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="M12" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="N12" s="16" t="s">
-        <v>85</v>
+        <v>88</v>
+      </c>
+      <c r="N12" s="16">
+        <v>6.08002515875E11</v>
       </c>
       <c r="O12" s="18"/>
       <c r="P12" s="13" t="s">
         <v>27</v>
       </c>
       <c r="Q12" s="14">
-        <v>12.0</v>
+        <v>13.0</v>
       </c>
       <c r="R12" s="5"/>
       <c r="S12" s="5"/>
@@ -2568,22 +2672,22 @@
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="15">
-        <v>46102.424570856485</v>
+        <v>46102.43412846065</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C13" s="16">
-        <v>24.0</v>
+        <v>32.0</v>
       </c>
       <c r="D13" s="16">
-        <v>9.480500716E9</v>
+        <v>9.845923471E9</v>
       </c>
       <c r="E13" s="16" t="s">
-        <v>87</v>
+        <v>50</v>
       </c>
       <c r="F13" s="16" t="s">
-        <v>88</v>
+        <v>43</v>
       </c>
       <c r="G13" s="16" t="s">
         <v>20</v>
@@ -2592,10 +2696,10 @@
         <v>37</v>
       </c>
       <c r="I13" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="J13" s="19" t="s">
         <v>90</v>
+      </c>
+      <c r="J13" s="16">
+        <v>94.0</v>
       </c>
       <c r="K13" s="16" t="s">
         <v>23</v>
@@ -2606,15 +2710,15 @@
       <c r="M13" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="N13" s="16">
-        <v>6.08002515875E11</v>
+      <c r="N13" s="16" t="s">
+        <v>93</v>
       </c>
       <c r="O13" s="18"/>
       <c r="P13" s="13" t="s">
         <v>27</v>
       </c>
       <c r="Q13" s="14">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="R13" s="5"/>
       <c r="S13" s="5"/>
@@ -2623,19 +2727,19 @@
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="15">
-        <v>46102.43412846065</v>
+        <v>46102.44132546296</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C14" s="16">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="D14" s="16">
-        <v>9.845923471E9</v>
+        <v>8.762763323E9</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="F14" s="16" t="s">
         <v>43</v>
@@ -2647,29 +2751,29 @@
         <v>37</v>
       </c>
       <c r="I14" s="16" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J14" s="16">
-        <v>94.0</v>
+        <v>11.0</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="L14" s="17" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M14" s="17" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N14" s="16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="O14" s="18"/>
       <c r="P14" s="13" t="s">
         <v>27</v>
       </c>
       <c r="Q14" s="14">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="R14" s="5"/>
       <c r="S14" s="5"/>
@@ -2678,22 +2782,22 @@
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="15">
-        <v>46102.44132546296</v>
+        <v>46102.47824483796</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C15" s="16">
-        <v>33.0</v>
+        <v>32.0</v>
       </c>
       <c r="D15" s="16">
-        <v>8.762763323E9</v>
+        <v>9.483064484E9</v>
       </c>
       <c r="E15" s="16" t="s">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="F15" s="16" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="G15" s="16" t="s">
         <v>20</v>
@@ -2702,29 +2806,29 @@
         <v>37</v>
       </c>
       <c r="I15" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="J15" s="16">
-        <v>11.0</v>
+        <v>100</v>
+      </c>
+      <c r="J15" s="19" t="s">
+        <v>101</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="L15" s="17" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M15" s="17" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N15" s="16" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="O15" s="18"/>
       <c r="P15" s="13" t="s">
         <v>27</v>
       </c>
       <c r="Q15" s="14">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="R15" s="5"/>
       <c r="S15" s="5"/>
@@ -2733,22 +2837,22 @@
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="15">
-        <v>46102.47824483796</v>
+        <v>46102.49769109953</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C16" s="16">
-        <v>32.0</v>
+        <v>36.0</v>
       </c>
       <c r="D16" s="16">
-        <v>9.483064484E9</v>
+        <v>9.481588529E9</v>
       </c>
       <c r="E16" s="16" t="s">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
       <c r="G16" s="16" t="s">
         <v>20</v>
@@ -2757,29 +2861,29 @@
         <v>37</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="J16" s="19" t="s">
-        <v>105</v>
+        <v>106</v>
+      </c>
+      <c r="J16" s="16">
+        <v>14.0</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="L16" s="17" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M16" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="N16" s="16" t="s">
         <v>108</v>
+      </c>
+      <c r="N16" s="16">
+        <v>6.44609859862E11</v>
       </c>
       <c r="O16" s="18"/>
       <c r="P16" s="13" t="s">
         <v>27</v>
       </c>
       <c r="Q16" s="14">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="R16" s="5"/>
       <c r="S16" s="5"/>
@@ -2788,22 +2892,22 @@
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="15">
-        <v>46102.49769109953</v>
+        <v>46102.562649837964</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>109</v>
       </c>
       <c r="C17" s="16">
-        <v>36.0</v>
+        <v>34.0</v>
       </c>
       <c r="D17" s="16">
-        <v>9.481588529E9</v>
+        <v>9.920648813E9</v>
       </c>
       <c r="E17" s="16" t="s">
-        <v>87</v>
+        <v>42</v>
       </c>
       <c r="F17" s="16" t="s">
-        <v>88</v>
+        <v>43</v>
       </c>
       <c r="G17" s="16" t="s">
         <v>20</v>
@@ -2814,11 +2918,11 @@
       <c r="I17" s="16" t="s">
         <v>110</v>
       </c>
-      <c r="J17" s="16">
-        <v>14.0</v>
+      <c r="J17" s="19" t="s">
+        <v>86</v>
       </c>
       <c r="K17" s="16" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="L17" s="17" t="s">
         <v>111</v>
@@ -2826,15 +2930,15 @@
       <c r="M17" s="17" t="s">
         <v>112</v>
       </c>
-      <c r="N17" s="16">
-        <v>6.44609859862E11</v>
+      <c r="N17" s="16" t="s">
+        <v>113</v>
       </c>
       <c r="O17" s="18"/>
       <c r="P17" s="13" t="s">
         <v>27</v>
       </c>
       <c r="Q17" s="14">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="R17" s="5"/>
       <c r="S17" s="5"/>
@@ -2843,22 +2947,22 @@
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="15">
-        <v>46102.562649837964</v>
+        <v>46102.63741747686</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C18" s="16">
-        <v>34.0</v>
+        <v>39.0</v>
       </c>
       <c r="D18" s="16">
-        <v>9.920648813E9</v>
+        <v>9.481988332E9</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="F18" s="16" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="G18" s="16" t="s">
         <v>20</v>
@@ -2867,29 +2971,29 @@
         <v>37</v>
       </c>
       <c r="I18" s="16" t="s">
-        <v>114</v>
-      </c>
-      <c r="J18" s="19" t="s">
-        <v>90</v>
+        <v>115</v>
+      </c>
+      <c r="J18" s="16">
+        <v>20.0</v>
       </c>
       <c r="K18" s="16" t="s">
         <v>32</v>
       </c>
       <c r="L18" s="17" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="M18" s="17" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N18" s="16" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O18" s="18"/>
       <c r="P18" s="13" t="s">
         <v>27</v>
       </c>
       <c r="Q18" s="14">
-        <v>18.0</v>
+        <v>19.0</v>
       </c>
       <c r="R18" s="5"/>
       <c r="S18" s="5"/>
@@ -2898,22 +3002,22 @@
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="15">
-        <v>46102.63741747686</v>
+        <v>46102.64167140046</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C19" s="16">
         <v>39.0</v>
       </c>
-      <c r="D19" s="16">
-        <v>9.481988332E9</v>
+      <c r="D19" s="16" t="s">
+        <v>120</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F19" s="16" t="s">
-        <v>88</v>
+        <v>43</v>
       </c>
       <c r="G19" s="16" t="s">
         <v>20</v>
@@ -2922,29 +3026,29 @@
         <v>37</v>
       </c>
       <c r="I19" s="16" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J19" s="16">
-        <v>20.0</v>
+        <v>22.0</v>
       </c>
       <c r="K19" s="16" t="s">
         <v>32</v>
       </c>
       <c r="L19" s="17" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="M19" s="17" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="N19" s="16" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="O19" s="18"/>
       <c r="P19" s="13" t="s">
         <v>27</v>
       </c>
       <c r="Q19" s="14">
-        <v>19.0</v>
+        <v>20.0</v>
       </c>
       <c r="R19" s="5"/>
       <c r="S19" s="5"/>
@@ -2953,53 +3057,53 @@
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="15">
-        <v>46102.64167140046</v>
+        <v>46102.64886339121</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C20" s="16">
-        <v>39.0</v>
-      </c>
-      <c r="D20" s="16" t="s">
-        <v>124</v>
+        <v>27.0</v>
+      </c>
+      <c r="D20" s="16">
+        <v>8.277793828E9</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F20" s="16" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="G20" s="16" t="s">
         <v>20</v>
       </c>
       <c r="H20" s="16" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="I20" s="16" t="s">
-        <v>125</v>
-      </c>
-      <c r="J20" s="16">
-        <v>22.0</v>
+        <v>126</v>
+      </c>
+      <c r="J20" s="19" t="s">
+        <v>26</v>
       </c>
       <c r="K20" s="16" t="s">
-        <v>32</v>
+        <v>127</v>
       </c>
       <c r="L20" s="17" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="M20" s="17" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="N20" s="16" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="O20" s="18"/>
       <c r="P20" s="13" t="s">
         <v>27</v>
       </c>
       <c r="Q20" s="14">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="R20" s="5"/>
       <c r="S20" s="5"/>
@@ -3008,53 +3112,53 @@
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="15">
-        <v>46102.64886339121</v>
+        <v>46102.678395104165</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C21" s="16">
-        <v>27.0</v>
+        <v>36.0</v>
       </c>
       <c r="D21" s="16">
-        <v>8.277793828E9</v>
+        <v>8.310187611E9</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F21" s="16" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="G21" s="16" t="s">
         <v>20</v>
       </c>
       <c r="H21" s="16" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="I21" s="16" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J21" s="19" t="s">
-        <v>26</v>
+        <v>133</v>
       </c>
       <c r="K21" s="16" t="s">
-        <v>131</v>
+        <v>57</v>
       </c>
       <c r="L21" s="17" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="M21" s="17" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="N21" s="16" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="O21" s="18"/>
       <c r="P21" s="13" t="s">
         <v>27</v>
       </c>
       <c r="Q21" s="14">
-        <v>21.0</v>
+        <v>22.0</v>
       </c>
       <c r="R21" s="5"/>
       <c r="S21" s="5"/>
@@ -3063,53 +3167,53 @@
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="15">
-        <v>46102.678395104165</v>
+        <v>46102.79322341435</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C22" s="16">
-        <v>36.0</v>
+        <v>29.0</v>
       </c>
       <c r="D22" s="16">
-        <v>8.310187611E9</v>
+        <v>9.48281672E9</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>87</v>
+        <v>138</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="G22" s="16" t="s">
         <v>20</v>
       </c>
       <c r="H22" s="16" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="I22" s="16" t="s">
-        <v>136</v>
-      </c>
-      <c r="J22" s="19" t="s">
-        <v>137</v>
+        <v>139</v>
+      </c>
+      <c r="J22" s="16">
+        <v>27.0</v>
       </c>
       <c r="K22" s="16" t="s">
         <v>57</v>
       </c>
       <c r="L22" s="17" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M22" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="N22" s="16" t="s">
-        <v>140</v>
+        <v>141</v>
+      </c>
+      <c r="N22" s="19" t="s">
+        <v>142</v>
       </c>
       <c r="O22" s="18"/>
       <c r="P22" s="13" t="s">
         <v>27</v>
       </c>
       <c r="Q22" s="14">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="R22" s="5"/>
       <c r="S22" s="5"/>
@@ -3118,53 +3222,53 @@
     </row>
     <row r="23" ht="22.5" customHeight="1">
       <c r="A23" s="15">
-        <v>46102.79322341435</v>
+        <v>46102.80097979167</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C23" s="16">
-        <v>29.0</v>
+        <v>28.0</v>
       </c>
       <c r="D23" s="16">
-        <v>9.48281672E9</v>
+        <v>8.431736726E9</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>142</v>
+        <v>50</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="G23" s="16" t="s">
         <v>20</v>
       </c>
       <c r="H23" s="16" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="I23" s="16" t="s">
-        <v>143</v>
-      </c>
-      <c r="J23" s="16">
-        <v>27.0</v>
+        <v>144</v>
+      </c>
+      <c r="J23" s="19" t="s">
+        <v>145</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="L23" s="17" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="M23" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="N23" s="19" t="s">
-        <v>146</v>
+        <v>147</v>
+      </c>
+      <c r="N23" s="16">
+        <v>7.8903209749E11</v>
       </c>
       <c r="O23" s="18"/>
       <c r="P23" s="13" t="s">
         <v>27</v>
       </c>
       <c r="Q23" s="14">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="R23" s="5"/>
       <c r="S23" s="5"/>
@@ -3173,53 +3277,51 @@
     </row>
     <row r="24" ht="22.5" customHeight="1">
       <c r="A24" s="15">
-        <v>46102.80097979167</v>
+        <v>46102.839051076386</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C24" s="16">
-        <v>28.0</v>
+        <v>26.0</v>
       </c>
       <c r="D24" s="16">
-        <v>8.431736726E9</v>
+        <v>8.277314932E9</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>50</v>
+        <v>138</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="G24" s="16" t="s">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="H24" s="16" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="I24" s="16" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J24" s="19" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="K24" s="16" t="s">
-        <v>131</v>
+        <v>23</v>
       </c>
       <c r="L24" s="17" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="M24" s="17" t="s">
-        <v>151</v>
-      </c>
-      <c r="N24" s="16">
-        <v>7.8903209749E11</v>
-      </c>
+        <v>153</v>
+      </c>
+      <c r="N24" s="18"/>
       <c r="O24" s="18"/>
       <c r="P24" s="13" t="s">
         <v>27</v>
       </c>
       <c r="Q24" s="14">
-        <v>24.0</v>
+        <v>25.0</v>
       </c>
       <c r="R24" s="5"/>
       <c r="S24" s="5"/>
@@ -3228,37 +3330,37 @@
     </row>
     <row r="25" ht="22.5" customHeight="1">
       <c r="A25" s="15">
-        <v>46102.839051076386</v>
+        <v>46102.847085057874</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C25" s="16">
-        <v>26.0</v>
+        <v>32.0</v>
       </c>
       <c r="D25" s="16">
-        <v>8.277314932E9</v>
+        <v>9.480157447E9</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="F25" s="16" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="G25" s="16" t="s">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="H25" s="16" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="I25" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="J25" s="19" t="s">
         <v>155</v>
       </c>
+      <c r="J25" s="16">
+        <v>18.0</v>
+      </c>
       <c r="K25" s="16" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="L25" s="17" t="s">
         <v>156</v>
@@ -3266,13 +3368,15 @@
       <c r="M25" s="17" t="s">
         <v>157</v>
       </c>
-      <c r="N25" s="18"/>
+      <c r="N25" s="16" t="s">
+        <v>158</v>
+      </c>
       <c r="O25" s="18"/>
       <c r="P25" s="13" t="s">
         <v>27</v>
       </c>
       <c r="Q25" s="14">
-        <v>25.0</v>
+        <v>26.0</v>
       </c>
       <c r="R25" s="5"/>
       <c r="S25" s="5"/>
@@ -3281,19 +3385,19 @@
     </row>
     <row r="26" ht="22.5" customHeight="1">
       <c r="A26" s="15">
-        <v>46102.847085057874</v>
+        <v>46102.87206900463</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C26" s="16">
-        <v>32.0</v>
-      </c>
-      <c r="D26" s="16">
-        <v>9.480157447E9</v>
+        <v>44.0</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>160</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="F26" s="16" t="s">
         <v>43</v>
@@ -3305,29 +3409,29 @@
         <v>37</v>
       </c>
       <c r="I26" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="J26" s="16">
-        <v>18.0</v>
+        <v>161</v>
+      </c>
+      <c r="J26" s="19" t="s">
+        <v>101</v>
       </c>
       <c r="K26" s="16" t="s">
         <v>32</v>
       </c>
       <c r="L26" s="17" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M26" s="17" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="N26" s="16" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O26" s="18"/>
       <c r="P26" s="13" t="s">
         <v>27</v>
       </c>
       <c r="Q26" s="14">
-        <v>26.0</v>
+        <v>27.0</v>
       </c>
       <c r="R26" s="5"/>
       <c r="S26" s="5"/>
@@ -3336,19 +3440,19 @@
     </row>
     <row r="27" ht="22.5" customHeight="1">
       <c r="A27" s="15">
-        <v>46102.87206900463</v>
+        <v>46102.87223923611</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C27" s="16">
-        <v>44.0</v>
-      </c>
-      <c r="D27" s="16" t="s">
-        <v>164</v>
+        <v>37.0</v>
+      </c>
+      <c r="D27" s="16">
+        <v>9.59043877E9</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>87</v>
+        <v>138</v>
       </c>
       <c r="F27" s="16" t="s">
         <v>43</v>
@@ -3360,29 +3464,29 @@
         <v>37</v>
       </c>
       <c r="I27" s="16" t="s">
-        <v>165</v>
-      </c>
-      <c r="J27" s="19" t="s">
-        <v>105</v>
+        <v>166</v>
+      </c>
+      <c r="J27" s="13" t="s">
+        <v>167</v>
       </c>
       <c r="K27" s="16" t="s">
-        <v>32</v>
+        <v>127</v>
       </c>
       <c r="L27" s="17" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M27" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="N27" s="16" t="s">
-        <v>168</v>
+        <v>169</v>
+      </c>
+      <c r="N27" s="16">
+        <v>6.44607223536E11</v>
       </c>
       <c r="O27" s="18"/>
       <c r="P27" s="13" t="s">
         <v>27</v>
       </c>
       <c r="Q27" s="14">
-        <v>27.0</v>
+        <v>28.0</v>
       </c>
       <c r="R27" s="5"/>
       <c r="S27" s="5"/>
@@ -3391,22 +3495,22 @@
     </row>
     <row r="28" ht="22.5" customHeight="1">
       <c r="A28" s="15">
-        <v>46102.87223923611</v>
+        <v>46102.90365760417</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C28" s="16">
-        <v>37.0</v>
+        <v>21.0</v>
       </c>
       <c r="D28" s="16">
-        <v>9.59043877E9</v>
+        <v>8.152916689E9</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>142</v>
+        <v>61</v>
       </c>
       <c r="F28" s="16" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="G28" s="16" t="s">
         <v>20</v>
@@ -3415,29 +3519,29 @@
         <v>37</v>
       </c>
       <c r="I28" s="16" t="s">
-        <v>170</v>
-      </c>
-      <c r="J28" s="13" t="s">
         <v>171</v>
       </c>
+      <c r="J28" s="16">
+        <v>18.0</v>
+      </c>
       <c r="K28" s="16" t="s">
-        <v>131</v>
+        <v>172</v>
       </c>
       <c r="L28" s="17" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M28" s="17" t="s">
-        <v>173</v>
-      </c>
-      <c r="N28" s="16">
-        <v>6.44607223536E11</v>
+        <v>174</v>
+      </c>
+      <c r="N28" s="16" t="s">
+        <v>175</v>
       </c>
       <c r="O28" s="18"/>
       <c r="P28" s="13" t="s">
         <v>27</v>
       </c>
       <c r="Q28" s="14">
-        <v>28.0</v>
+        <v>29.0</v>
       </c>
       <c r="R28" s="5"/>
       <c r="S28" s="5"/>
@@ -3446,22 +3550,22 @@
     </row>
     <row r="29" ht="22.5" customHeight="1">
       <c r="A29" s="15">
-        <v>46102.90365760417</v>
+        <v>46102.973693865744</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C29" s="16">
-        <v>21.0</v>
+        <v>24.0</v>
       </c>
       <c r="D29" s="16">
-        <v>8.152916689E9</v>
+        <v>9.483303103E9</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="F29" s="16" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G29" s="16" t="s">
         <v>20</v>
@@ -3470,29 +3574,27 @@
         <v>37</v>
       </c>
       <c r="I29" s="16" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="J29" s="16">
-        <v>18.0</v>
+        <v>22.0</v>
       </c>
       <c r="K29" s="16" t="s">
-        <v>176</v>
+        <v>32</v>
       </c>
       <c r="L29" s="17" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M29" s="17" t="s">
-        <v>178</v>
-      </c>
-      <c r="N29" s="16" t="s">
         <v>179</v>
       </c>
+      <c r="N29" s="18"/>
       <c r="O29" s="18"/>
       <c r="P29" s="13" t="s">
         <v>27</v>
       </c>
       <c r="Q29" s="14">
-        <v>29.0</v>
+        <v>30.0</v>
       </c>
       <c r="R29" s="5"/>
       <c r="S29" s="5"/>
@@ -3501,37 +3603,37 @@
     </row>
     <row r="30" ht="22.5" customHeight="1">
       <c r="A30" s="15">
-        <v>46102.973693865744</v>
+        <v>46102.99283037037</v>
       </c>
       <c r="B30" s="7" t="s">
         <v>180</v>
       </c>
       <c r="C30" s="16">
-        <v>24.0</v>
+        <v>21.0</v>
       </c>
       <c r="D30" s="16">
-        <v>9.483303103E9</v>
+        <v>9.141594772E9</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="F30" s="16" t="s">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="G30" s="16" t="s">
         <v>20</v>
       </c>
       <c r="H30" s="16" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="I30" s="16" t="s">
         <v>181</v>
       </c>
       <c r="J30" s="16">
-        <v>22.0</v>
+        <v>20.0</v>
       </c>
       <c r="K30" s="16" t="s">
-        <v>32</v>
+        <v>172</v>
       </c>
       <c r="L30" s="17" t="s">
         <v>182</v>
@@ -3539,13 +3641,15 @@
       <c r="M30" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="N30" s="18"/>
+      <c r="N30" s="16" t="s">
+        <v>184</v>
+      </c>
       <c r="O30" s="18"/>
       <c r="P30" s="13" t="s">
         <v>27</v>
       </c>
       <c r="Q30" s="14">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
       <c r="R30" s="5"/>
       <c r="S30" s="5"/>
@@ -3554,53 +3658,53 @@
     </row>
     <row r="31" ht="22.5" customHeight="1">
       <c r="A31" s="15">
-        <v>46102.99283037037</v>
+        <v>46103.000396296295</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C31" s="16">
-        <v>21.0</v>
+        <v>20.0</v>
       </c>
       <c r="D31" s="16">
-        <v>9.141594772E9</v>
+        <v>7.019286836E9</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="F31" s="16" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="G31" s="16" t="s">
         <v>20</v>
       </c>
       <c r="H31" s="16" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="I31" s="16" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J31" s="16">
-        <v>20.0</v>
+        <v>27.0</v>
       </c>
       <c r="K31" s="16" t="s">
-        <v>176</v>
+        <v>57</v>
       </c>
       <c r="L31" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M31" s="17" t="s">
-        <v>187</v>
-      </c>
-      <c r="N31" s="16" t="s">
         <v>188</v>
+      </c>
+      <c r="N31" s="16">
+        <v>6.08097730524E11</v>
       </c>
       <c r="O31" s="18"/>
       <c r="P31" s="13" t="s">
         <v>27</v>
       </c>
       <c r="Q31" s="14">
-        <v>31.0</v>
+        <v>32.0</v>
       </c>
       <c r="R31" s="5"/>
       <c r="S31" s="5"/>
@@ -3609,19 +3713,19 @@
     </row>
     <row r="32" ht="22.5" customHeight="1">
       <c r="A32" s="15">
-        <v>46103.000396296295</v>
+        <v>46103.02590607639</v>
       </c>
       <c r="B32" s="7" t="s">
         <v>189</v>
       </c>
       <c r="C32" s="16">
-        <v>20.0</v>
+        <v>26.0</v>
       </c>
       <c r="D32" s="16">
-        <v>7.019286836E9</v>
+        <v>9.972788263E9</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="F32" s="16" t="s">
         <v>43</v>
@@ -3635,11 +3739,11 @@
       <c r="I32" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="J32" s="16">
-        <v>27.0</v>
+      <c r="J32" s="19" t="s">
+        <v>101</v>
       </c>
       <c r="K32" s="16" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="L32" s="17" t="s">
         <v>191</v>
@@ -3647,15 +3751,15 @@
       <c r="M32" s="17" t="s">
         <v>192</v>
       </c>
-      <c r="N32" s="16">
-        <v>6.08097730524E11</v>
+      <c r="N32" s="16" t="s">
+        <v>193</v>
       </c>
       <c r="O32" s="18"/>
       <c r="P32" s="13" t="s">
         <v>27</v>
       </c>
       <c r="Q32" s="14">
-        <v>32.0</v>
+        <v>33.0</v>
       </c>
       <c r="R32" s="5"/>
       <c r="S32" s="5"/>
@@ -3664,19 +3768,19 @@
     </row>
     <row r="33" ht="22.5" customHeight="1">
       <c r="A33" s="15">
-        <v>46103.02590607639</v>
+        <v>46103.42829592593</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C33" s="16">
-        <v>26.0</v>
+        <v>42.0</v>
       </c>
       <c r="D33" s="16">
-        <v>9.972788263E9</v>
+        <v>8.762098441E9</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>42</v>
+        <v>83</v>
       </c>
       <c r="F33" s="16" t="s">
         <v>43</v>
@@ -3688,29 +3792,29 @@
         <v>37</v>
       </c>
       <c r="I33" s="16" t="s">
-        <v>194</v>
-      </c>
-      <c r="J33" s="19" t="s">
-        <v>105</v>
+        <v>195</v>
+      </c>
+      <c r="J33" s="16">
+        <v>11.0</v>
       </c>
       <c r="K33" s="16" t="s">
-        <v>23</v>
+        <v>127</v>
       </c>
       <c r="L33" s="17" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="M33" s="17" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="N33" s="16" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O33" s="18"/>
       <c r="P33" s="13" t="s">
         <v>27</v>
       </c>
       <c r="Q33" s="14">
-        <v>33.0</v>
+        <v>34.0</v>
       </c>
       <c r="R33" s="5"/>
       <c r="S33" s="5"/>
@@ -3719,19 +3823,19 @@
     </row>
     <row r="34" ht="22.5" customHeight="1">
       <c r="A34" s="15">
-        <v>46103.42829592593</v>
+        <v>46103.441093113426</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C34" s="16">
-        <v>42.0</v>
+        <v>41.0</v>
       </c>
       <c r="D34" s="16">
-        <v>8.762098441E9</v>
+        <v>9.448759319E9</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>87</v>
+        <v>200</v>
       </c>
       <c r="F34" s="16" t="s">
         <v>43</v>
@@ -3743,29 +3847,29 @@
         <v>37</v>
       </c>
       <c r="I34" s="16" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="J34" s="16">
-        <v>11.0</v>
+        <v>25.0</v>
       </c>
       <c r="K34" s="16" t="s">
-        <v>131</v>
+        <v>32</v>
       </c>
       <c r="L34" s="17" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="M34" s="17" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="N34" s="16" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="O34" s="18"/>
       <c r="P34" s="13" t="s">
         <v>27</v>
       </c>
       <c r="Q34" s="14">
-        <v>34.0</v>
+        <v>35.0</v>
       </c>
       <c r="R34" s="5"/>
       <c r="S34" s="5"/>
@@ -3774,53 +3878,53 @@
     </row>
     <row r="35" ht="22.5" customHeight="1">
       <c r="A35" s="15">
-        <v>46103.441093113426</v>
+        <v>46103.452146724536</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="C35" s="16">
-        <v>41.0</v>
+        <v>25.0</v>
       </c>
       <c r="D35" s="16">
-        <v>9.448759319E9</v>
+        <v>9.481181696E9</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>204</v>
+        <v>83</v>
       </c>
       <c r="F35" s="16" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="G35" s="16" t="s">
         <v>20</v>
       </c>
       <c r="H35" s="16" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="I35" s="16" t="s">
-        <v>205</v>
-      </c>
-      <c r="J35" s="16">
-        <v>25.0</v>
+        <v>206</v>
+      </c>
+      <c r="J35" s="19" t="s">
+        <v>101</v>
       </c>
       <c r="K35" s="16" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="L35" s="17" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="M35" s="17" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="N35" s="16" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="O35" s="18"/>
       <c r="P35" s="13" t="s">
         <v>27</v>
       </c>
       <c r="Q35" s="14">
-        <v>35.0</v>
+        <v>36.0</v>
       </c>
       <c r="R35" s="5"/>
       <c r="S35" s="5"/>
@@ -3829,19 +3933,19 @@
     </row>
     <row r="36" ht="22.5" customHeight="1">
       <c r="A36" s="15">
-        <v>46103.452146724536</v>
+        <v>46103.46026305556</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C36" s="16">
-        <v>25.0</v>
+        <v>38.0</v>
       </c>
       <c r="D36" s="16">
-        <v>9.481181696E9</v>
+        <v>9.448009193E9</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>87</v>
+        <v>42</v>
       </c>
       <c r="F36" s="16" t="s">
         <v>19</v>
@@ -3853,29 +3957,29 @@
         <v>21</v>
       </c>
       <c r="I36" s="16" t="s">
-        <v>210</v>
-      </c>
-      <c r="J36" s="19" t="s">
-        <v>105</v>
+        <v>211</v>
+      </c>
+      <c r="J36" s="16" t="s">
+        <v>212</v>
       </c>
       <c r="K36" s="16" t="s">
         <v>57</v>
       </c>
       <c r="L36" s="17" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="M36" s="17" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="N36" s="16" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="O36" s="18"/>
       <c r="P36" s="13" t="s">
         <v>27</v>
       </c>
       <c r="Q36" s="14">
-        <v>36.0</v>
+        <v>37.0</v>
       </c>
       <c r="R36" s="5"/>
       <c r="S36" s="5"/>
@@ -3884,53 +3988,53 @@
     </row>
     <row r="37" ht="22.5" customHeight="1">
       <c r="A37" s="15">
-        <v>46103.46026305556</v>
+        <v>46103.471992418985</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C37" s="16">
-        <v>38.0</v>
+        <v>25.0</v>
       </c>
       <c r="D37" s="16">
-        <v>9.448009193E9</v>
+        <v>7.89920033E9</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F37" s="16" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="G37" s="16" t="s">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="H37" s="16" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="I37" s="16" t="s">
-        <v>215</v>
-      </c>
-      <c r="J37" s="16" t="s">
-        <v>216</v>
+        <v>217</v>
+      </c>
+      <c r="J37" s="16">
+        <v>22.0</v>
       </c>
       <c r="K37" s="16" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="L37" s="17" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M37" s="17" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N37" s="16" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O37" s="18"/>
       <c r="P37" s="13" t="s">
         <v>27</v>
       </c>
       <c r="Q37" s="14">
-        <v>37.0</v>
+        <v>38.0</v>
       </c>
       <c r="R37" s="5"/>
       <c r="S37" s="5"/>
@@ -3939,53 +4043,53 @@
     </row>
     <row r="38" ht="22.5" customHeight="1">
       <c r="A38" s="15">
-        <v>46103.471992418985</v>
+        <v>46103.534131423614</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C38" s="16">
         <v>25.0</v>
       </c>
       <c r="D38" s="16">
-        <v>7.89920033E9</v>
+        <v>9.482654189E9</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>36</v>
+        <v>138</v>
       </c>
       <c r="F38" s="16" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="G38" s="16" t="s">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="H38" s="16" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="I38" s="16" t="s">
         <v>221</v>
       </c>
-      <c r="J38" s="16">
-        <v>22.0</v>
+      <c r="J38" s="19" t="s">
+        <v>26</v>
       </c>
       <c r="K38" s="16" t="s">
-        <v>23</v>
+        <v>222</v>
       </c>
       <c r="L38" s="17" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M38" s="17" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="N38" s="16" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="O38" s="18"/>
       <c r="P38" s="13" t="s">
         <v>27</v>
       </c>
       <c r="Q38" s="14">
-        <v>38.0</v>
+        <v>39.0</v>
       </c>
       <c r="R38" s="5"/>
       <c r="S38" s="5"/>
@@ -3994,37 +4098,37 @@
     </row>
     <row r="39" ht="22.5" customHeight="1">
       <c r="A39" s="15">
-        <v>46103.534131423614</v>
-      </c>
-      <c r="B39" s="7" t="s">
+        <v>46103.55557842593</v>
+      </c>
+      <c r="B39" s="16" t="s">
         <v>225</v>
       </c>
       <c r="C39" s="16">
-        <v>25.0</v>
-      </c>
-      <c r="D39" s="16">
-        <v>9.482654189E9</v>
+        <v>33.0</v>
+      </c>
+      <c r="D39" s="16" t="s">
+        <v>226</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="F39" s="16" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
       <c r="G39" s="16" t="s">
         <v>20</v>
       </c>
       <c r="H39" s="16" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="I39" s="16" t="s">
-        <v>225</v>
-      </c>
-      <c r="J39" s="19" t="s">
-        <v>26</v>
+        <v>190</v>
+      </c>
+      <c r="J39" s="16">
+        <v>56.0</v>
       </c>
       <c r="K39" s="16" t="s">
-        <v>226</v>
+        <v>57</v>
       </c>
       <c r="L39" s="17" t="s">
         <v>227</v>
@@ -4033,14 +4137,12 @@
         <v>228</v>
       </c>
       <c r="N39" s="16" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="O39" s="18"/>
-      <c r="P39" s="13" t="s">
-        <v>27</v>
-      </c>
+      <c r="P39" s="18"/>
       <c r="Q39" s="14">
-        <v>39.0</v>
+        <v>40.0</v>
       </c>
       <c r="R39" s="5"/>
       <c r="S39" s="5"/>
@@ -4049,22 +4151,22 @@
     </row>
     <row r="40" ht="22.5" customHeight="1">
       <c r="A40" s="15">
-        <v>46103.55557842593</v>
+        <v>46103.56289596065</v>
       </c>
       <c r="B40" s="16" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C40" s="16">
-        <v>33.0</v>
-      </c>
-      <c r="D40" s="16" t="s">
-        <v>230</v>
+        <v>18.0</v>
+      </c>
+      <c r="D40" s="16">
+        <v>8.762908848E9</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>87</v>
+        <v>42</v>
       </c>
       <c r="F40" s="16" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G40" s="16" t="s">
         <v>20</v>
@@ -4073,27 +4175,27 @@
         <v>37</v>
       </c>
       <c r="I40" s="16" t="s">
-        <v>194</v>
+        <v>231</v>
       </c>
       <c r="J40" s="16">
-        <v>56.0</v>
+        <v>2.0</v>
       </c>
       <c r="K40" s="16" t="s">
-        <v>57</v>
+        <v>172</v>
       </c>
       <c r="L40" s="17" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M40" s="17" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="N40" s="16" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="O40" s="18"/>
       <c r="P40" s="18"/>
       <c r="Q40" s="14">
-        <v>40.0</v>
+        <v>41.0</v>
       </c>
       <c r="R40" s="5"/>
       <c r="S40" s="5"/>
@@ -4102,22 +4204,22 @@
     </row>
     <row r="41" ht="22.5" customHeight="1">
       <c r="A41" s="15">
-        <v>46103.56289596065</v>
+        <v>46103.59041957176</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C41" s="16">
-        <v>18.0</v>
+        <v>45.0</v>
       </c>
       <c r="D41" s="16">
-        <v>8.762908848E9</v>
+        <v>8.762634307E9</v>
       </c>
       <c r="E41" s="16" t="s">
         <v>42</v>
       </c>
       <c r="F41" s="16" t="s">
-        <v>88</v>
+        <v>43</v>
       </c>
       <c r="G41" s="16" t="s">
         <v>20</v>
@@ -4126,27 +4228,27 @@
         <v>37</v>
       </c>
       <c r="I41" s="16" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="J41" s="16">
-        <v>2.0</v>
+        <v>14.0</v>
       </c>
       <c r="K41" s="16" t="s">
-        <v>176</v>
+        <v>23</v>
       </c>
       <c r="L41" s="17" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="M41" s="17" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="N41" s="16" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="O41" s="18"/>
       <c r="P41" s="18"/>
       <c r="Q41" s="14">
-        <v>41.0</v>
+        <v>42.0</v>
       </c>
       <c r="R41" s="5"/>
       <c r="S41" s="5"/>
@@ -4155,22 +4257,22 @@
     </row>
     <row r="42" ht="22.5" customHeight="1">
       <c r="A42" s="15">
-        <v>46103.59041957176</v>
+        <v>46103.71109726852</v>
       </c>
       <c r="B42" s="16" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C42" s="16">
-        <v>45.0</v>
+        <v>31.0</v>
       </c>
       <c r="D42" s="16">
-        <v>8.762634307E9</v>
+        <v>9.481434425E9</v>
       </c>
       <c r="E42" s="16" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F42" s="16" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="G42" s="16" t="s">
         <v>20</v>
@@ -4179,27 +4281,27 @@
         <v>37</v>
       </c>
       <c r="I42" s="16" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J42" s="16">
-        <v>14.0</v>
+        <v>29.0</v>
       </c>
       <c r="K42" s="16" t="s">
         <v>23</v>
       </c>
       <c r="L42" s="17" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M42" s="17" t="s">
-        <v>242</v>
-      </c>
-      <c r="N42" s="16" t="s">
         <v>243</v>
+      </c>
+      <c r="N42" s="16">
+        <v>6.08161927388E11</v>
       </c>
       <c r="O42" s="18"/>
       <c r="P42" s="18"/>
       <c r="Q42" s="14">
-        <v>42.0</v>
+        <v>43.0</v>
       </c>
       <c r="R42" s="5"/>
       <c r="S42" s="5"/>
@@ -4208,22 +4310,22 @@
     </row>
     <row r="43" ht="22.5" customHeight="1">
       <c r="A43" s="15">
-        <v>46103.71109726852</v>
+        <v>46103.78890800926</v>
       </c>
       <c r="B43" s="16" t="s">
         <v>244</v>
       </c>
       <c r="C43" s="16">
-        <v>31.0</v>
+        <v>27.0</v>
       </c>
       <c r="D43" s="16">
-        <v>9.481434425E9</v>
+        <v>9.483474589E9</v>
       </c>
       <c r="E43" s="16" t="s">
         <v>36</v>
       </c>
       <c r="F43" s="16" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="G43" s="16" t="s">
         <v>20</v>
@@ -4235,7 +4337,7 @@
         <v>245</v>
       </c>
       <c r="J43" s="16">
-        <v>29.0</v>
+        <v>9.0</v>
       </c>
       <c r="K43" s="16" t="s">
         <v>23</v>
@@ -4246,13 +4348,13 @@
       <c r="M43" s="17" t="s">
         <v>247</v>
       </c>
-      <c r="N43" s="16">
-        <v>6.08161927388E11</v>
+      <c r="N43" s="16" t="s">
+        <v>248</v>
       </c>
       <c r="O43" s="18"/>
       <c r="P43" s="18"/>
       <c r="Q43" s="14">
-        <v>43.0</v>
+        <v>44.0</v>
       </c>
       <c r="R43" s="5"/>
       <c r="S43" s="5"/>
@@ -4261,22 +4363,22 @@
     </row>
     <row r="44" ht="22.5" customHeight="1">
       <c r="A44" s="15">
-        <v>46103.78890800926</v>
+        <v>46103.850049155095</v>
       </c>
       <c r="B44" s="16" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C44" s="16">
-        <v>27.0</v>
+        <v>16.0</v>
       </c>
       <c r="D44" s="16">
-        <v>9.483474589E9</v>
+        <v>9.481862646E9</v>
       </c>
       <c r="E44" s="16" t="s">
-        <v>36</v>
+        <v>250</v>
       </c>
       <c r="F44" s="16" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="G44" s="16" t="s">
         <v>20</v>
@@ -4285,27 +4387,27 @@
         <v>37</v>
       </c>
       <c r="I44" s="16" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="J44" s="16">
-        <v>9.0</v>
+        <v>44.0</v>
       </c>
       <c r="K44" s="16" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="L44" s="17" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M44" s="17" t="s">
-        <v>251</v>
-      </c>
-      <c r="N44" s="16" t="s">
-        <v>252</v>
+        <v>253</v>
+      </c>
+      <c r="N44" s="16">
+        <v>6.44767503962E11</v>
       </c>
       <c r="O44" s="18"/>
       <c r="P44" s="18"/>
       <c r="Q44" s="14">
-        <v>44.0</v>
+        <v>45.0</v>
       </c>
       <c r="R44" s="5"/>
       <c r="S44" s="5"/>
@@ -4314,25 +4416,25 @@
     </row>
     <row r="45" ht="22.5" customHeight="1">
       <c r="A45" s="15">
-        <v>46103.850049155095</v>
+        <v>46103.871615578704</v>
       </c>
       <c r="B45" s="16" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C45" s="16">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="D45" s="16">
-        <v>9.481862646E9</v>
+        <v>9.110429344E9</v>
       </c>
       <c r="E45" s="16" t="s">
-        <v>254</v>
+        <v>36</v>
       </c>
       <c r="F45" s="16" t="s">
-        <v>88</v>
+        <v>43</v>
       </c>
       <c r="G45" s="16" t="s">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="H45" s="16" t="s">
         <v>37</v>
@@ -4340,11 +4442,11 @@
       <c r="I45" s="16" t="s">
         <v>255</v>
       </c>
-      <c r="J45" s="16">
-        <v>44.0</v>
+      <c r="J45" s="19" t="s">
+        <v>151</v>
       </c>
       <c r="K45" s="16" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="L45" s="17" t="s">
         <v>256</v>
@@ -4352,13 +4454,13 @@
       <c r="M45" s="17" t="s">
         <v>257</v>
       </c>
-      <c r="N45" s="16">
-        <v>6.44767503962E11</v>
+      <c r="N45" s="16" t="s">
+        <v>258</v>
       </c>
       <c r="O45" s="18"/>
       <c r="P45" s="18"/>
       <c r="Q45" s="14">
-        <v>45.0</v>
+        <v>46.0</v>
       </c>
       <c r="R45" s="5"/>
       <c r="S45" s="5"/>
@@ -4367,51 +4469,51 @@
     </row>
     <row r="46" ht="22.5" customHeight="1">
       <c r="A46" s="15">
-        <v>46103.871615578704</v>
+        <v>46103.88576951389</v>
       </c>
       <c r="B46" s="16" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C46" s="16">
-        <v>17.0</v>
+        <v>41.0</v>
       </c>
       <c r="D46" s="16">
-        <v>9.110429344E9</v>
+        <v>9.481130252E9</v>
       </c>
       <c r="E46" s="16" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F46" s="16" t="s">
-        <v>43</v>
+        <v>260</v>
       </c>
       <c r="G46" s="16" t="s">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="H46" s="16" t="s">
         <v>37</v>
       </c>
       <c r="I46" s="16" t="s">
-        <v>259</v>
-      </c>
-      <c r="J46" s="19" t="s">
-        <v>155</v>
+        <v>261</v>
+      </c>
+      <c r="J46" s="16">
+        <v>0.0</v>
       </c>
       <c r="K46" s="16" t="s">
         <v>23</v>
       </c>
       <c r="L46" s="17" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M46" s="17" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="N46" s="16" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="O46" s="18"/>
       <c r="P46" s="18"/>
       <c r="Q46" s="14">
-        <v>46.0</v>
+        <v>47.0</v>
       </c>
       <c r="R46" s="5"/>
       <c r="S46" s="5"/>
@@ -4420,22 +4522,22 @@
     </row>
     <row r="47" ht="22.5" customHeight="1">
       <c r="A47" s="15">
-        <v>46103.88576951389</v>
+        <v>46103.88841773148</v>
       </c>
       <c r="B47" s="16" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C47" s="16">
-        <v>41.0</v>
+        <v>25.0</v>
       </c>
       <c r="D47" s="16">
-        <v>9.481130252E9</v>
+        <v>8.277568729E9</v>
       </c>
       <c r="E47" s="16" t="s">
-        <v>42</v>
+        <v>138</v>
       </c>
       <c r="F47" s="16" t="s">
-        <v>264</v>
+        <v>43</v>
       </c>
       <c r="G47" s="16" t="s">
         <v>20</v>
@@ -4444,27 +4546,27 @@
         <v>37</v>
       </c>
       <c r="I47" s="16" t="s">
-        <v>265</v>
-      </c>
-      <c r="J47" s="16">
-        <v>0.0</v>
+        <v>266</v>
+      </c>
+      <c r="J47" s="19" t="s">
+        <v>267</v>
       </c>
       <c r="K47" s="16" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="L47" s="17" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="M47" s="17" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N47" s="16" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O47" s="18"/>
       <c r="P47" s="18"/>
       <c r="Q47" s="14">
-        <v>47.0</v>
+        <v>48.0</v>
       </c>
       <c r="R47" s="5"/>
       <c r="S47" s="5"/>
@@ -4473,19 +4575,19 @@
     </row>
     <row r="48" ht="22.5" customHeight="1">
       <c r="A48" s="15">
-        <v>46103.88841773148</v>
+        <v>46103.89859025463</v>
       </c>
       <c r="B48" s="16" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C48" s="16">
-        <v>25.0</v>
+        <v>39.0</v>
       </c>
       <c r="D48" s="16">
-        <v>8.277568729E9</v>
+        <v>9.481109932E9</v>
       </c>
       <c r="E48" s="16" t="s">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="F48" s="16" t="s">
         <v>43</v>
@@ -4497,27 +4599,27 @@
         <v>37</v>
       </c>
       <c r="I48" s="16" t="s">
-        <v>270</v>
-      </c>
-      <c r="J48" s="19" t="s">
-        <v>271</v>
+        <v>272</v>
+      </c>
+      <c r="J48" s="16">
+        <v>108.0</v>
       </c>
       <c r="K48" s="16" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="L48" s="17" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M48" s="17" t="s">
-        <v>273</v>
-      </c>
-      <c r="N48" s="16" t="s">
         <v>274</v>
+      </c>
+      <c r="N48" s="16">
+        <v>3.46137127914E11</v>
       </c>
       <c r="O48" s="18"/>
       <c r="P48" s="18"/>
       <c r="Q48" s="14">
-        <v>48.0</v>
+        <v>49.0</v>
       </c>
       <c r="R48" s="5"/>
       <c r="S48" s="5"/>
@@ -4526,51 +4628,51 @@
     </row>
     <row r="49" ht="22.5" customHeight="1">
       <c r="A49" s="15">
-        <v>46103.89859025463</v>
+        <v>46103.91416940972</v>
       </c>
       <c r="B49" s="16" t="s">
         <v>275</v>
       </c>
       <c r="C49" s="16">
-        <v>39.0</v>
+        <v>38.0</v>
       </c>
       <c r="D49" s="16">
-        <v>9.481109932E9</v>
+        <v>9.48110996E9</v>
       </c>
       <c r="E49" s="16" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="F49" s="16" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="G49" s="16" t="s">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="H49" s="16" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="I49" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="J49" s="16">
+        <v>29.0</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="L49" s="17" t="s">
         <v>276</v>
       </c>
-      <c r="J49" s="16">
-        <v>108.0</v>
-      </c>
-      <c r="K49" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="L49" s="17" t="s">
+      <c r="M49" s="17" t="s">
         <v>277</v>
       </c>
-      <c r="M49" s="17" t="s">
+      <c r="N49" s="16" t="s">
         <v>278</v>
-      </c>
-      <c r="N49" s="16">
-        <v>3.46137127914E11</v>
       </c>
       <c r="O49" s="18"/>
       <c r="P49" s="18"/>
       <c r="Q49" s="14">
-        <v>49.0</v>
+        <v>50.0</v>
       </c>
       <c r="R49" s="5"/>
       <c r="S49" s="5"/>
@@ -4579,51 +4681,51 @@
     </row>
     <row r="50" ht="22.5" customHeight="1">
       <c r="A50" s="15">
-        <v>46103.91416940972</v>
+        <v>46103.92549395833</v>
       </c>
       <c r="B50" s="16" t="s">
         <v>279</v>
       </c>
       <c r="C50" s="16">
-        <v>38.0</v>
+        <v>22.0</v>
       </c>
       <c r="D50" s="16">
-        <v>9.48110996E9</v>
+        <v>9.481862646E9</v>
       </c>
       <c r="E50" s="16" t="s">
-        <v>61</v>
+        <v>250</v>
       </c>
       <c r="F50" s="16" t="s">
         <v>19</v>
       </c>
       <c r="G50" s="16" t="s">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="H50" s="16" t="s">
         <v>21</v>
       </c>
       <c r="I50" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="J50" s="16">
-        <v>29.0</v>
+        <v>280</v>
+      </c>
+      <c r="J50" s="19" t="s">
+        <v>145</v>
       </c>
       <c r="K50" s="16" t="s">
         <v>32</v>
       </c>
       <c r="L50" s="17" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M50" s="17" t="s">
-        <v>281</v>
-      </c>
-      <c r="N50" s="16" t="s">
         <v>282</v>
+      </c>
+      <c r="N50" s="16">
+        <v>6.44799208811E11</v>
       </c>
       <c r="O50" s="18"/>
       <c r="P50" s="18"/>
       <c r="Q50" s="14">
-        <v>50.0</v>
+        <v>51.0</v>
       </c>
       <c r="R50" s="5"/>
       <c r="S50" s="5"/>
@@ -4632,19 +4734,19 @@
     </row>
     <row r="51" ht="22.5" customHeight="1">
       <c r="A51" s="15">
-        <v>46103.92549395833</v>
+        <v>46103.982147013885</v>
       </c>
       <c r="B51" s="16" t="s">
         <v>283</v>
       </c>
       <c r="C51" s="16">
-        <v>22.0</v>
+        <v>17.0</v>
       </c>
       <c r="D51" s="16">
-        <v>9.481862646E9</v>
+        <v>9.606330117E9</v>
       </c>
       <c r="E51" s="16" t="s">
-        <v>254</v>
+        <v>61</v>
       </c>
       <c r="F51" s="16" t="s">
         <v>19</v>
@@ -4659,10 +4761,10 @@
         <v>284</v>
       </c>
       <c r="J51" s="19" t="s">
-        <v>149</v>
+        <v>63</v>
       </c>
       <c r="K51" s="16" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="L51" s="17" t="s">
         <v>285</v>
@@ -4670,13 +4772,13 @@
       <c r="M51" s="17" t="s">
         <v>286</v>
       </c>
-      <c r="N51" s="16">
-        <v>6.44799208811E11</v>
+      <c r="N51" s="16" t="s">
+        <v>287</v>
       </c>
       <c r="O51" s="18"/>
       <c r="P51" s="18"/>
       <c r="Q51" s="14">
-        <v>51.0</v>
+        <v>52.0</v>
       </c>
       <c r="R51" s="5"/>
       <c r="S51" s="5"/>
@@ -4685,19 +4787,19 @@
     </row>
     <row r="52" ht="22.5" customHeight="1">
       <c r="A52" s="15">
-        <v>46103.982147013885</v>
+        <v>46103.98512327546</v>
       </c>
       <c r="B52" s="16" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C52" s="16">
-        <v>17.0</v>
+        <v>25.0</v>
       </c>
       <c r="D52" s="16">
-        <v>9.606330117E9</v>
+        <v>6.361961853E9</v>
       </c>
       <c r="E52" s="16" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="F52" s="16" t="s">
         <v>19</v>
@@ -4709,27 +4811,27 @@
         <v>21</v>
       </c>
       <c r="I52" s="16" t="s">
-        <v>288</v>
-      </c>
-      <c r="J52" s="19" t="s">
-        <v>63</v>
+        <v>289</v>
+      </c>
+      <c r="J52" s="16">
+        <v>19.0</v>
       </c>
       <c r="K52" s="16" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="L52" s="17" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M52" s="17" t="s">
-        <v>290</v>
-      </c>
-      <c r="N52" s="16" t="s">
         <v>291</v>
+      </c>
+      <c r="N52" s="16">
+        <v>6.08172806218E11</v>
       </c>
       <c r="O52" s="18"/>
       <c r="P52" s="18"/>
       <c r="Q52" s="14">
-        <v>52.0</v>
+        <v>53.0</v>
       </c>
       <c r="R52" s="5"/>
       <c r="S52" s="5"/>
@@ -4738,19 +4840,19 @@
     </row>
     <row r="53" ht="22.5" customHeight="1">
       <c r="A53" s="15">
-        <v>46103.98512327546</v>
+        <v>46104.41497385417</v>
       </c>
       <c r="B53" s="16" t="s">
         <v>292</v>
       </c>
       <c r="C53" s="16">
-        <v>25.0</v>
-      </c>
-      <c r="D53" s="16">
-        <v>6.361961853E9</v>
+        <v>30.0</v>
+      </c>
+      <c r="D53" s="16" t="s">
+        <v>293</v>
       </c>
       <c r="E53" s="16" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="F53" s="16" t="s">
         <v>19</v>
@@ -4762,27 +4864,27 @@
         <v>21</v>
       </c>
       <c r="I53" s="16" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="J53" s="16">
-        <v>19.0</v>
+        <v>18.0</v>
       </c>
       <c r="K53" s="16" t="s">
         <v>23</v>
       </c>
       <c r="L53" s="17" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="M53" s="17" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N53" s="16">
-        <v>6.08172806218E11</v>
+        <v>3.81386584955E11</v>
       </c>
       <c r="O53" s="18"/>
       <c r="P53" s="18"/>
       <c r="Q53" s="14">
-        <v>53.0</v>
+        <v>54.0</v>
       </c>
       <c r="R53" s="5"/>
       <c r="S53" s="5"/>
@@ -4791,51 +4893,51 @@
     </row>
     <row r="54" ht="22.5" customHeight="1">
       <c r="A54" s="15">
-        <v>46104.41497385417</v>
+        <v>46104.42279599537</v>
       </c>
       <c r="B54" s="16" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C54" s="16">
-        <v>30.0</v>
+        <v>17.0</v>
       </c>
       <c r="D54" s="16" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="E54" s="16" t="s">
         <v>36</v>
       </c>
       <c r="F54" s="16" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="G54" s="16" t="s">
         <v>20</v>
       </c>
       <c r="H54" s="16" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="I54" s="16" t="s">
-        <v>298</v>
-      </c>
-      <c r="J54" s="16">
-        <v>18.0</v>
+        <v>299</v>
+      </c>
+      <c r="J54" s="19" t="s">
+        <v>86</v>
       </c>
       <c r="K54" s="16" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="L54" s="17" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M54" s="17" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N54" s="16">
-        <v>3.81386584955E11</v>
+        <v>3.9524057182E11</v>
       </c>
       <c r="O54" s="18"/>
       <c r="P54" s="18"/>
       <c r="Q54" s="14">
-        <v>54.0</v>
+        <v>55.0</v>
       </c>
       <c r="R54" s="5"/>
       <c r="S54" s="5"/>
@@ -4844,51 +4946,51 @@
     </row>
     <row r="55" ht="22.5" customHeight="1">
       <c r="A55" s="15">
-        <v>46104.42279599537</v>
+        <v>46104.42597133102</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C55" s="16">
-        <v>17.0</v>
-      </c>
-      <c r="D55" s="16" t="s">
-        <v>302</v>
+        <v>31.0</v>
+      </c>
+      <c r="D55" s="16">
+        <v>9.483613712E9</v>
       </c>
       <c r="E55" s="16" t="s">
-        <v>36</v>
+        <v>138</v>
       </c>
       <c r="F55" s="16" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="G55" s="16" t="s">
         <v>20</v>
       </c>
       <c r="H55" s="16" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="I55" s="16" t="s">
+        <v>302</v>
+      </c>
+      <c r="J55" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="L55" s="17" t="s">
         <v>303</v>
       </c>
-      <c r="J55" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="K55" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="L55" s="17" t="s">
+      <c r="M55" s="17" t="s">
         <v>304</v>
       </c>
-      <c r="M55" s="17" t="s">
+      <c r="N55" s="16" t="s">
         <v>305</v>
-      </c>
-      <c r="N55" s="16">
-        <v>3.9524057182E11</v>
       </c>
       <c r="O55" s="18"/>
       <c r="P55" s="18"/>
       <c r="Q55" s="14">
-        <v>55.0</v>
+        <v>56.0</v>
       </c>
       <c r="R55" s="5"/>
       <c r="S55" s="5"/>
@@ -4897,51 +4999,51 @@
     </row>
     <row r="56" ht="22.5" customHeight="1">
       <c r="A56" s="15">
-        <v>46104.42597133102</v>
+        <v>46104.43026435185</v>
       </c>
       <c r="B56" s="16" t="s">
         <v>306</v>
       </c>
       <c r="C56" s="16">
-        <v>31.0</v>
-      </c>
-      <c r="D56" s="16">
-        <v>9.483613712E9</v>
+        <v>36.0</v>
+      </c>
+      <c r="D56" s="16" t="s">
+        <v>307</v>
       </c>
       <c r="E56" s="16" t="s">
-        <v>142</v>
+        <v>55</v>
       </c>
       <c r="F56" s="16" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
       <c r="G56" s="16" t="s">
         <v>20</v>
       </c>
       <c r="H56" s="16" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="I56" s="16" t="s">
-        <v>306</v>
-      </c>
-      <c r="J56" s="19" t="s">
-        <v>63</v>
+        <v>308</v>
+      </c>
+      <c r="J56" s="16">
+        <v>10.0</v>
       </c>
       <c r="K56" s="16" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="L56" s="17" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="M56" s="17" t="s">
-        <v>308</v>
-      </c>
-      <c r="N56" s="16" t="s">
-        <v>309</v>
+        <v>310</v>
+      </c>
+      <c r="N56" s="16">
+        <v>3.23064487139E11</v>
       </c>
       <c r="O56" s="18"/>
       <c r="P56" s="18"/>
       <c r="Q56" s="14">
-        <v>56.0</v>
+        <v>57.0</v>
       </c>
       <c r="R56" s="5"/>
       <c r="S56" s="5"/>
@@ -4950,37 +5052,37 @@
     </row>
     <row r="57" ht="22.5" customHeight="1">
       <c r="A57" s="15">
-        <v>46104.43026435185</v>
+        <v>46104.43936664352</v>
       </c>
       <c r="B57" s="16" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C57" s="16">
-        <v>36.0</v>
-      </c>
-      <c r="D57" s="16" t="s">
-        <v>311</v>
+        <v>19.0</v>
+      </c>
+      <c r="D57" s="16">
+        <v>8.08829604E9</v>
       </c>
       <c r="E57" s="16" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="F57" s="16" t="s">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="G57" s="16" t="s">
         <v>20</v>
       </c>
       <c r="H57" s="16" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="I57" s="16" t="s">
         <v>312</v>
       </c>
       <c r="J57" s="16">
-        <v>10.0</v>
+        <v>16.0</v>
       </c>
       <c r="K57" s="16" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="L57" s="17" t="s">
         <v>313</v>
@@ -4988,13 +5090,13 @@
       <c r="M57" s="17" t="s">
         <v>314</v>
       </c>
-      <c r="N57" s="16">
-        <v>3.23064487139E11</v>
+      <c r="N57" s="16" t="s">
+        <v>315</v>
       </c>
       <c r="O57" s="18"/>
       <c r="P57" s="18"/>
       <c r="Q57" s="14">
-        <v>57.0</v>
+        <v>58.0</v>
       </c>
       <c r="R57" s="5"/>
       <c r="S57" s="5"/>
@@ -5003,19 +5105,19 @@
     </row>
     <row r="58" ht="22.5" customHeight="1">
       <c r="A58" s="15">
-        <v>46104.43936664352</v>
+        <v>46104.45988934027</v>
       </c>
       <c r="B58" s="16" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C58" s="16">
-        <v>19.0</v>
-      </c>
-      <c r="D58" s="16">
-        <v>8.08829604E9</v>
+        <v>30.0</v>
+      </c>
+      <c r="D58" s="16" t="s">
+        <v>317</v>
       </c>
       <c r="E58" s="16" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="F58" s="16" t="s">
         <v>19</v>
@@ -5024,30 +5126,30 @@
         <v>20</v>
       </c>
       <c r="H58" s="16" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="I58" s="16" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="J58" s="16">
-        <v>16.0</v>
+        <v>25.0</v>
       </c>
       <c r="K58" s="16" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="L58" s="17" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="M58" s="17" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="N58" s="16" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="O58" s="18"/>
       <c r="P58" s="18"/>
       <c r="Q58" s="14">
-        <v>58.0</v>
+        <v>59.0</v>
       </c>
       <c r="R58" s="5"/>
       <c r="S58" s="5"/>
@@ -5056,51 +5158,51 @@
     </row>
     <row r="59" ht="22.5" customHeight="1">
       <c r="A59" s="15">
-        <v>46104.45988934027</v>
+        <v>46104.46055996528</v>
       </c>
       <c r="B59" s="16" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C59" s="16">
-        <v>30.0</v>
-      </c>
-      <c r="D59" s="16" t="s">
-        <v>321</v>
+        <v>22.0</v>
+      </c>
+      <c r="D59" s="16">
+        <v>9.482602961E9</v>
       </c>
       <c r="E59" s="16" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="F59" s="16" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
       <c r="G59" s="16" t="s">
-        <v>20</v>
+        <v>323</v>
       </c>
       <c r="H59" s="16" t="s">
         <v>37</v>
       </c>
       <c r="I59" s="16" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="J59" s="16">
-        <v>25.0</v>
+        <v>18.0</v>
       </c>
       <c r="K59" s="16" t="s">
         <v>57</v>
       </c>
       <c r="L59" s="17" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="M59" s="17" t="s">
-        <v>324</v>
-      </c>
-      <c r="N59" s="16" t="s">
-        <v>325</v>
+        <v>326</v>
+      </c>
+      <c r="N59" s="16">
+        <v>2.02467989528E11</v>
       </c>
       <c r="O59" s="18"/>
       <c r="P59" s="18"/>
       <c r="Q59" s="14">
-        <v>59.0</v>
+        <v>60.0</v>
       </c>
       <c r="R59" s="5"/>
       <c r="S59" s="5"/>
@@ -5109,51 +5211,51 @@
     </row>
     <row r="60" ht="22.5" customHeight="1">
       <c r="A60" s="15">
-        <v>46104.46055996528</v>
+        <v>46104.46488784722</v>
       </c>
       <c r="B60" s="16" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C60" s="16">
-        <v>22.0</v>
+        <v>25.0</v>
       </c>
       <c r="D60" s="16">
-        <v>9.482602961E9</v>
+        <v>9.449417296E9</v>
       </c>
       <c r="E60" s="16" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="F60" s="16" t="s">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="G60" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H60" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I60" s="16" t="s">
         <v>327</v>
       </c>
-      <c r="H60" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="I60" s="16" t="s">
-        <v>328</v>
-      </c>
       <c r="J60" s="16">
-        <v>18.0</v>
+        <v>26.0</v>
       </c>
       <c r="K60" s="16" t="s">
         <v>57</v>
       </c>
       <c r="L60" s="17" t="s">
+        <v>328</v>
+      </c>
+      <c r="M60" s="17" t="s">
         <v>329</v>
       </c>
-      <c r="M60" s="17" t="s">
-        <v>330</v>
-      </c>
       <c r="N60" s="16">
-        <v>2.02467989528E11</v>
+        <v>6.08217110623E11</v>
       </c>
       <c r="O60" s="18"/>
       <c r="P60" s="18"/>
       <c r="Q60" s="14">
-        <v>60.0</v>
+        <v>61.0</v>
       </c>
       <c r="R60" s="5"/>
       <c r="S60" s="5"/>
@@ -5162,34 +5264,34 @@
     </row>
     <row r="61" ht="22.5" customHeight="1">
       <c r="A61" s="15">
-        <v>46104.46488784722</v>
+        <v>46104.47144248843</v>
       </c>
       <c r="B61" s="16" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C61" s="16">
-        <v>25.0</v>
+        <v>42.0</v>
       </c>
       <c r="D61" s="16">
-        <v>9.449417296E9</v>
+        <v>8.762383104E9</v>
       </c>
       <c r="E61" s="16" t="s">
         <v>55</v>
       </c>
       <c r="F61" s="16" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="G61" s="16" t="s">
         <v>20</v>
       </c>
       <c r="H61" s="16" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="I61" s="16" t="s">
         <v>331</v>
       </c>
       <c r="J61" s="16">
-        <v>26.0</v>
+        <v>34.0</v>
       </c>
       <c r="K61" s="16" t="s">
         <v>57</v>
@@ -5201,12 +5303,12 @@
         <v>333</v>
       </c>
       <c r="N61" s="16">
-        <v>6.08217110623E11</v>
+        <v>6.44897835798E11</v>
       </c>
       <c r="O61" s="18"/>
       <c r="P61" s="18"/>
       <c r="Q61" s="14">
-        <v>61.0</v>
+        <v>62.0</v>
       </c>
       <c r="R61" s="5"/>
       <c r="S61" s="5"/>
@@ -5215,34 +5317,34 @@
     </row>
     <row r="62" ht="22.5" customHeight="1">
       <c r="A62" s="15">
-        <v>46104.47144248843</v>
+        <v>46104.47650885417</v>
       </c>
       <c r="B62" s="16" t="s">
         <v>334</v>
       </c>
       <c r="C62" s="16">
-        <v>42.0</v>
+        <v>39.0</v>
       </c>
       <c r="D62" s="16">
-        <v>8.762383104E9</v>
+        <v>8.762559939E9</v>
       </c>
       <c r="E62" s="16" t="s">
         <v>55</v>
       </c>
       <c r="F62" s="16" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="G62" s="16" t="s">
         <v>20</v>
       </c>
       <c r="H62" s="16" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="I62" s="16" t="s">
         <v>335</v>
       </c>
-      <c r="J62" s="16">
-        <v>34.0</v>
+      <c r="J62" s="19" t="s">
+        <v>63</v>
       </c>
       <c r="K62" s="16" t="s">
         <v>57</v>
@@ -5254,12 +5356,12 @@
         <v>337</v>
       </c>
       <c r="N62" s="16">
-        <v>6.44897835798E11</v>
+        <v>6.44856629241E11</v>
       </c>
       <c r="O62" s="18"/>
       <c r="P62" s="18"/>
       <c r="Q62" s="14">
-        <v>62.0</v>
+        <v>63.0</v>
       </c>
       <c r="R62" s="5"/>
       <c r="S62" s="5"/>
@@ -5268,34 +5370,34 @@
     </row>
     <row r="63" ht="22.5" customHeight="1">
       <c r="A63" s="15">
-        <v>46104.47650885417</v>
+        <v>46104.48011070602</v>
       </c>
       <c r="B63" s="16" t="s">
         <v>338</v>
       </c>
       <c r="C63" s="16">
-        <v>39.0</v>
+        <v>20.0</v>
       </c>
       <c r="D63" s="16">
-        <v>8.762559939E9</v>
+        <v>9.48289308E9</v>
       </c>
       <c r="E63" s="16" t="s">
         <v>55</v>
       </c>
       <c r="F63" s="16" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="G63" s="16" t="s">
         <v>20</v>
       </c>
       <c r="H63" s="16" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="I63" s="16" t="s">
         <v>339</v>
       </c>
-      <c r="J63" s="19" t="s">
-        <v>63</v>
+      <c r="J63" s="16">
+        <v>31.0</v>
       </c>
       <c r="K63" s="16" t="s">
         <v>57</v>
@@ -5307,12 +5409,12 @@
         <v>341</v>
       </c>
       <c r="N63" s="16">
-        <v>6.44856629241E11</v>
+        <v>6.44895337878E11</v>
       </c>
       <c r="O63" s="18"/>
       <c r="P63" s="18"/>
       <c r="Q63" s="14">
-        <v>63.0</v>
+        <v>64.0</v>
       </c>
       <c r="R63" s="5"/>
       <c r="S63" s="5"/>
@@ -5321,25 +5423,25 @@
     </row>
     <row r="64" ht="22.5" customHeight="1">
       <c r="A64" s="15">
-        <v>46104.48011070602</v>
+        <v>46104.48489824074</v>
       </c>
       <c r="B64" s="16" t="s">
         <v>342</v>
       </c>
       <c r="C64" s="16">
-        <v>20.0</v>
+        <v>43.0</v>
       </c>
       <c r="D64" s="16">
-        <v>9.48289308E9</v>
+        <v>7.507509971E9</v>
       </c>
       <c r="E64" s="16" t="s">
         <v>55</v>
       </c>
       <c r="F64" s="16" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="G64" s="16" t="s">
-        <v>20</v>
+        <v>323</v>
       </c>
       <c r="H64" s="16" t="s">
         <v>37</v>
@@ -5348,10 +5450,10 @@
         <v>343</v>
       </c>
       <c r="J64" s="16">
-        <v>31.0</v>
+        <v>21.0</v>
       </c>
       <c r="K64" s="16" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="L64" s="17" t="s">
         <v>344</v>
@@ -5360,12 +5462,12 @@
         <v>345</v>
       </c>
       <c r="N64" s="16">
-        <v>6.44895337878E11</v>
+        <v>6.44826733446E11</v>
       </c>
       <c r="O64" s="18"/>
       <c r="P64" s="18"/>
       <c r="Q64" s="14">
-        <v>64.0</v>
+        <v>65.0</v>
       </c>
       <c r="R64" s="5"/>
       <c r="S64" s="5"/>
@@ -5374,25 +5476,25 @@
     </row>
     <row r="65" ht="22.5" customHeight="1">
       <c r="A65" s="15">
-        <v>46104.48489824074</v>
+        <v>46104.49068898148</v>
       </c>
       <c r="B65" s="16" t="s">
         <v>346</v>
       </c>
       <c r="C65" s="16">
-        <v>43.0</v>
+        <v>36.0</v>
       </c>
       <c r="D65" s="16">
-        <v>7.507509971E9</v>
+        <v>7.975484061E9</v>
       </c>
       <c r="E65" s="16" t="s">
-        <v>55</v>
+        <v>83</v>
       </c>
       <c r="F65" s="16" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G65" s="16" t="s">
-        <v>327</v>
+        <v>20</v>
       </c>
       <c r="H65" s="16" t="s">
         <v>37</v>
@@ -5401,10 +5503,10 @@
         <v>347</v>
       </c>
       <c r="J65" s="16">
-        <v>21.0</v>
+        <v>44.0</v>
       </c>
       <c r="K65" s="16" t="s">
-        <v>23</v>
+        <v>127</v>
       </c>
       <c r="L65" s="17" t="s">
         <v>348</v>
@@ -5413,12 +5515,12 @@
         <v>349</v>
       </c>
       <c r="N65" s="16">
-        <v>6.44826733446E11</v>
+        <v>6.08205928151E11</v>
       </c>
       <c r="O65" s="18"/>
       <c r="P65" s="18"/>
       <c r="Q65" s="14">
-        <v>65.0</v>
+        <v>66.0</v>
       </c>
       <c r="R65" s="5"/>
       <c r="S65" s="5"/>
@@ -5427,22 +5529,22 @@
     </row>
     <row r="66" ht="22.5" customHeight="1">
       <c r="A66" s="15">
-        <v>46104.49068898148</v>
+        <v>46104.50410734954</v>
       </c>
       <c r="B66" s="16" t="s">
         <v>350</v>
       </c>
       <c r="C66" s="16">
-        <v>36.0</v>
+        <v>38.0</v>
       </c>
       <c r="D66" s="16">
-        <v>7.975484061E9</v>
+        <v>8.762758945E9</v>
       </c>
       <c r="E66" s="16" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F66" s="16" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G66" s="16" t="s">
         <v>20</v>
@@ -5454,10 +5556,10 @@
         <v>351</v>
       </c>
       <c r="J66" s="16">
-        <v>44.0</v>
+        <v>42.0</v>
       </c>
       <c r="K66" s="16" t="s">
-        <v>131</v>
+        <v>32</v>
       </c>
       <c r="L66" s="17" t="s">
         <v>352</v>
@@ -5466,12 +5568,12 @@
         <v>353</v>
       </c>
       <c r="N66" s="16">
-        <v>6.08205928151E11</v>
+        <v>6.08205955604E11</v>
       </c>
       <c r="O66" s="18"/>
       <c r="P66" s="18"/>
       <c r="Q66" s="14">
-        <v>66.0</v>
+        <v>67.0</v>
       </c>
       <c r="R66" s="5"/>
       <c r="S66" s="5"/>
@@ -5480,51 +5582,51 @@
     </row>
     <row r="67" ht="22.5" customHeight="1">
       <c r="A67" s="15">
-        <v>46104.50410734954</v>
+        <v>46104.50986413195</v>
       </c>
       <c r="B67" s="16" t="s">
         <v>354</v>
       </c>
       <c r="C67" s="16">
-        <v>38.0</v>
-      </c>
-      <c r="D67" s="16">
-        <v>8.762758945E9</v>
+        <v>21.0</v>
+      </c>
+      <c r="D67" s="16" t="s">
+        <v>355</v>
       </c>
       <c r="E67" s="16" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="F67" s="16" t="s">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="G67" s="16" t="s">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="H67" s="16" t="s">
         <v>37</v>
       </c>
       <c r="I67" s="16" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J67" s="16">
-        <v>42.0</v>
+        <v>19.0</v>
       </c>
       <c r="K67" s="16" t="s">
-        <v>32</v>
+        <v>172</v>
       </c>
       <c r="L67" s="17" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M67" s="17" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N67" s="16">
-        <v>6.08205955604E11</v>
+        <v>2.79875519256E11</v>
       </c>
       <c r="O67" s="18"/>
       <c r="P67" s="18"/>
       <c r="Q67" s="14">
-        <v>67.0</v>
+        <v>68.0</v>
       </c>
       <c r="R67" s="5"/>
       <c r="S67" s="5"/>
@@ -5533,51 +5635,51 @@
     </row>
     <row r="68" ht="22.5" customHeight="1">
       <c r="A68" s="15">
-        <v>46104.50986413195</v>
+        <v>46104.51493157407</v>
       </c>
       <c r="B68" s="16" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C68" s="16">
-        <v>21.0</v>
+        <v>45.0</v>
       </c>
       <c r="D68" s="16" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E68" s="16" t="s">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="F68" s="16" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
       <c r="G68" s="16" t="s">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="H68" s="16" t="s">
         <v>37</v>
       </c>
       <c r="I68" s="16" t="s">
-        <v>360</v>
-      </c>
-      <c r="J68" s="16">
-        <v>19.0</v>
+        <v>361</v>
+      </c>
+      <c r="J68" s="19" t="s">
+        <v>26</v>
       </c>
       <c r="K68" s="16" t="s">
-        <v>176</v>
+        <v>127</v>
       </c>
       <c r="L68" s="17" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M68" s="17" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N68" s="16">
-        <v>2.79875519256E11</v>
+        <v>9.77195058008E11</v>
       </c>
       <c r="O68" s="18"/>
       <c r="P68" s="18"/>
       <c r="Q68" s="14">
-        <v>68.0</v>
+        <v>69.0</v>
       </c>
       <c r="R68" s="5"/>
       <c r="S68" s="5"/>
@@ -5586,22 +5688,22 @@
     </row>
     <row r="69" ht="22.5" customHeight="1">
       <c r="A69" s="15">
-        <v>46104.51493157407</v>
+        <v>46104.52836552083</v>
       </c>
       <c r="B69" s="16" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C69" s="16">
-        <v>45.0</v>
-      </c>
-      <c r="D69" s="16" t="s">
-        <v>364</v>
+        <v>43.0</v>
+      </c>
+      <c r="D69" s="16">
+        <v>9.449390824E9</v>
       </c>
       <c r="E69" s="16" t="s">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="F69" s="16" t="s">
-        <v>88</v>
+        <v>43</v>
       </c>
       <c r="G69" s="16" t="s">
         <v>20</v>
@@ -5613,10 +5715,10 @@
         <v>365</v>
       </c>
       <c r="J69" s="19" t="s">
-        <v>26</v>
+        <v>73</v>
       </c>
       <c r="K69" s="16" t="s">
-        <v>131</v>
+        <v>32</v>
       </c>
       <c r="L69" s="17" t="s">
         <v>366</v>
@@ -5625,12 +5727,12 @@
         <v>367</v>
       </c>
       <c r="N69" s="16">
-        <v>9.77195058008E11</v>
+        <v>5.65210505615E11</v>
       </c>
       <c r="O69" s="18"/>
       <c r="P69" s="18"/>
       <c r="Q69" s="14">
-        <v>69.0</v>
+        <v>70.0</v>
       </c>
       <c r="R69" s="5"/>
       <c r="S69" s="5"/>
@@ -5639,34 +5741,34 @@
     </row>
     <row r="70" ht="22.5" customHeight="1">
       <c r="A70" s="15">
-        <v>46104.52836552083</v>
+        <v>46104.532047071756</v>
       </c>
       <c r="B70" s="16" t="s">
         <v>368</v>
       </c>
       <c r="C70" s="16">
-        <v>43.0</v>
+        <v>37.0</v>
       </c>
       <c r="D70" s="16">
-        <v>9.449390824E9</v>
+        <v>9.482817011E9</v>
       </c>
       <c r="E70" s="16" t="s">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="F70" s="16" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="G70" s="16" t="s">
         <v>20</v>
       </c>
       <c r="H70" s="16" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="I70" s="16" t="s">
         <v>369</v>
       </c>
       <c r="J70" s="19" t="s">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="K70" s="16" t="s">
         <v>32</v>
@@ -5678,12 +5780,12 @@
         <v>371</v>
       </c>
       <c r="N70" s="16">
-        <v>5.65210505615E11</v>
+        <v>6.44886522321E11</v>
       </c>
       <c r="O70" s="18"/>
       <c r="P70" s="18"/>
       <c r="Q70" s="14">
-        <v>70.0</v>
+        <v>71.0</v>
       </c>
       <c r="R70" s="5"/>
       <c r="S70" s="5"/>
@@ -5692,16 +5794,16 @@
     </row>
     <row r="71" ht="22.5" customHeight="1">
       <c r="A71" s="15">
-        <v>46104.532047071756</v>
+        <v>46104.53527719907</v>
       </c>
       <c r="B71" s="16" t="s">
         <v>372</v>
       </c>
       <c r="C71" s="16">
-        <v>37.0</v>
+        <v>40.0</v>
       </c>
       <c r="D71" s="16">
-        <v>9.482817011E9</v>
+        <v>9.449574581E9</v>
       </c>
       <c r="E71" s="16" t="s">
         <v>55</v>
@@ -5719,10 +5821,10 @@
         <v>373</v>
       </c>
       <c r="J71" s="19" t="s">
-        <v>137</v>
+        <v>26</v>
       </c>
       <c r="K71" s="16" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="L71" s="17" t="s">
         <v>374</v>
@@ -5731,12 +5833,12 @@
         <v>375</v>
       </c>
       <c r="N71" s="16">
-        <v>6.44886522321E11</v>
+        <v>6.44817844572E11</v>
       </c>
       <c r="O71" s="18"/>
       <c r="P71" s="18"/>
       <c r="Q71" s="14">
-        <v>71.0</v>
+        <v>72.0</v>
       </c>
       <c r="R71" s="5"/>
       <c r="S71" s="5"/>
@@ -5745,13 +5847,13 @@
     </row>
     <row r="72" ht="22.5" customHeight="1">
       <c r="A72" s="15">
-        <v>46104.53527719907</v>
+        <v>46104.53849818287</v>
       </c>
       <c r="B72" s="16" t="s">
         <v>376</v>
       </c>
       <c r="C72" s="16">
-        <v>40.0</v>
+        <v>13.0</v>
       </c>
       <c r="D72" s="16">
         <v>9.449574581E9</v>
@@ -5760,22 +5862,22 @@
         <v>55</v>
       </c>
       <c r="F72" s="16" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="G72" s="16" t="s">
         <v>20</v>
       </c>
       <c r="H72" s="16" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="I72" s="16" t="s">
         <v>377</v>
       </c>
-      <c r="J72" s="19" t="s">
-        <v>26</v>
+      <c r="J72" s="16">
+        <v>13.0</v>
       </c>
       <c r="K72" s="16" t="s">
-        <v>23</v>
+        <v>222</v>
       </c>
       <c r="L72" s="17" t="s">
         <v>378</v>
@@ -5784,12 +5886,12 @@
         <v>379</v>
       </c>
       <c r="N72" s="16">
-        <v>6.44817844572E11</v>
+        <v>6.44827141799E11</v>
       </c>
       <c r="O72" s="18"/>
       <c r="P72" s="18"/>
       <c r="Q72" s="14">
-        <v>72.0</v>
+        <v>73.0</v>
       </c>
       <c r="R72" s="5"/>
       <c r="S72" s="5"/>
@@ -5798,22 +5900,22 @@
     </row>
     <row r="73" ht="22.5" customHeight="1">
       <c r="A73" s="15">
-        <v>46104.53849818287</v>
+        <v>46104.553243159724</v>
       </c>
       <c r="B73" s="16" t="s">
         <v>380</v>
       </c>
       <c r="C73" s="16">
-        <v>13.0</v>
+        <v>32.0</v>
       </c>
       <c r="D73" s="16">
-        <v>9.449574581E9</v>
+        <v>7.48372899E9</v>
       </c>
       <c r="E73" s="16" t="s">
         <v>55</v>
       </c>
       <c r="F73" s="16" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="G73" s="16" t="s">
         <v>20</v>
@@ -5825,10 +5927,10 @@
         <v>381</v>
       </c>
       <c r="J73" s="16">
-        <v>13.0</v>
+        <v>29.0</v>
       </c>
       <c r="K73" s="16" t="s">
-        <v>226</v>
+        <v>23</v>
       </c>
       <c r="L73" s="17" t="s">
         <v>382</v>
@@ -5837,12 +5939,12 @@
         <v>383</v>
       </c>
       <c r="N73" s="16">
-        <v>6.44827141799E11</v>
+        <v>1.20451042238E11</v>
       </c>
       <c r="O73" s="18"/>
       <c r="P73" s="18"/>
       <c r="Q73" s="14">
-        <v>73.0</v>
+        <v>74.0</v>
       </c>
       <c r="R73" s="5"/>
       <c r="S73" s="5"/>
@@ -5851,22 +5953,22 @@
     </row>
     <row r="74" ht="22.5" customHeight="1">
       <c r="A74" s="15">
-        <v>46104.553243159724</v>
+        <v>46104.58469640046</v>
       </c>
       <c r="B74" s="16" t="s">
         <v>384</v>
       </c>
       <c r="C74" s="16">
-        <v>32.0</v>
+        <v>30.0</v>
       </c>
       <c r="D74" s="16">
-        <v>7.48372899E9</v>
+        <v>7.020599753E9</v>
       </c>
       <c r="E74" s="16" t="s">
         <v>55</v>
       </c>
       <c r="F74" s="16" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="G74" s="16" t="s">
         <v>20</v>
@@ -5875,27 +5977,27 @@
         <v>37</v>
       </c>
       <c r="I74" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="J74" s="16">
+        <v>21.0</v>
+      </c>
+      <c r="K74" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="L74" s="17" t="s">
         <v>385</v>
       </c>
-      <c r="J74" s="16">
-        <v>29.0</v>
-      </c>
-      <c r="K74" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="L74" s="17" t="s">
+      <c r="M74" s="17" t="s">
         <v>386</v>
       </c>
-      <c r="M74" s="17" t="s">
-        <v>387</v>
-      </c>
       <c r="N74" s="16">
-        <v>1.20451042238E11</v>
+        <v>6.08290725766E11</v>
       </c>
       <c r="O74" s="18"/>
       <c r="P74" s="18"/>
       <c r="Q74" s="14">
-        <v>74.0</v>
+        <v>75.0</v>
       </c>
       <c r="R74" s="5"/>
       <c r="S74" s="5"/>
@@ -5904,22 +6006,22 @@
     </row>
     <row r="75" ht="22.5" customHeight="1">
       <c r="A75" s="15">
-        <v>46104.58469640046</v>
+        <v>46104.596843321764</v>
       </c>
       <c r="B75" s="16" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C75" s="16">
-        <v>30.0</v>
+        <v>23.0</v>
       </c>
       <c r="D75" s="16">
-        <v>7.020599753E9</v>
+        <v>6.36062561E9</v>
       </c>
       <c r="E75" s="16" t="s">
         <v>55</v>
       </c>
       <c r="F75" s="16" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="G75" s="16" t="s">
         <v>20</v>
@@ -5928,13 +6030,13 @@
         <v>37</v>
       </c>
       <c r="I75" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="J75" s="16">
-        <v>21.0</v>
+        <v>388</v>
+      </c>
+      <c r="J75" s="19" t="s">
+        <v>267</v>
       </c>
       <c r="K75" s="16" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="L75" s="17" t="s">
         <v>389</v>
@@ -5943,12 +6045,12 @@
         <v>390</v>
       </c>
       <c r="N75" s="16">
-        <v>6.08290725766E11</v>
+        <v>6.08285045353E11</v>
       </c>
       <c r="O75" s="18"/>
       <c r="P75" s="18"/>
       <c r="Q75" s="14">
-        <v>75.0</v>
+        <v>76.0</v>
       </c>
       <c r="R75" s="5"/>
       <c r="S75" s="5"/>
@@ -5957,34 +6059,34 @@
     </row>
     <row r="76" ht="22.5" customHeight="1">
       <c r="A76" s="15">
-        <v>46104.596843321764</v>
+        <v>46104.59883322917</v>
       </c>
       <c r="B76" s="16" t="s">
         <v>391</v>
       </c>
       <c r="C76" s="16">
-        <v>23.0</v>
+        <v>30.0</v>
       </c>
       <c r="D76" s="16">
-        <v>6.36062561E9</v>
+        <v>8.76293983E9</v>
       </c>
       <c r="E76" s="16" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="F76" s="16" t="s">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="G76" s="16" t="s">
         <v>20</v>
       </c>
       <c r="H76" s="16" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="I76" s="16" t="s">
         <v>392</v>
       </c>
-      <c r="J76" s="19" t="s">
-        <v>271</v>
+      <c r="J76" s="16">
+        <v>18.0</v>
       </c>
       <c r="K76" s="16" t="s">
         <v>23</v>
@@ -5995,13 +6097,13 @@
       <c r="M76" s="17" t="s">
         <v>394</v>
       </c>
-      <c r="N76" s="16">
-        <v>6.08285045353E11</v>
+      <c r="N76" s="16" t="s">
+        <v>395</v>
       </c>
       <c r="O76" s="18"/>
       <c r="P76" s="18"/>
       <c r="Q76" s="14">
-        <v>76.0</v>
+        <v>77.0</v>
       </c>
       <c r="R76" s="5"/>
       <c r="S76" s="5"/>
@@ -6010,51 +6112,51 @@
     </row>
     <row r="77" ht="22.5" customHeight="1">
       <c r="A77" s="15">
-        <v>46104.59883322917</v>
+        <v>46104.60333938657</v>
       </c>
       <c r="B77" s="16" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C77" s="16">
-        <v>30.0</v>
+        <v>42.0</v>
       </c>
       <c r="D77" s="16">
-        <v>8.76293983E9</v>
+        <v>9.149567404E9</v>
       </c>
       <c r="E77" s="16" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="F77" s="16" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="G77" s="16" t="s">
         <v>20</v>
       </c>
       <c r="H77" s="16" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="I77" s="16" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="J77" s="16">
-        <v>18.0</v>
+        <v>26.0</v>
       </c>
       <c r="K77" s="16" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="L77" s="17" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M77" s="17" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N77" s="16" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O77" s="18"/>
       <c r="P77" s="18"/>
       <c r="Q77" s="14">
-        <v>77.0</v>
+        <v>78.0</v>
       </c>
       <c r="R77" s="5"/>
       <c r="S77" s="5"/>
@@ -6063,51 +6165,51 @@
     </row>
     <row r="78" ht="22.5" customHeight="1">
       <c r="A78" s="15">
-        <v>46104.60333938657</v>
+        <v>46104.60472307871</v>
       </c>
       <c r="B78" s="16" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C78" s="16">
-        <v>42.0</v>
+        <v>29.0</v>
       </c>
       <c r="D78" s="16">
-        <v>9.149567404E9</v>
+        <v>9.483455859E9</v>
       </c>
       <c r="E78" s="16" t="s">
-        <v>42</v>
+        <v>200</v>
       </c>
       <c r="F78" s="16" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="G78" s="16" t="s">
         <v>20</v>
       </c>
       <c r="H78" s="16" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="I78" s="16" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J78" s="16">
-        <v>26.0</v>
+        <v>16.0</v>
       </c>
       <c r="K78" s="16" t="s">
         <v>32</v>
       </c>
       <c r="L78" s="17" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="M78" s="17" t="s">
-        <v>403</v>
-      </c>
-      <c r="N78" s="16" t="s">
         <v>404</v>
+      </c>
+      <c r="N78" s="16">
+        <v>6.08206770571E11</v>
       </c>
       <c r="O78" s="18"/>
       <c r="P78" s="18"/>
       <c r="Q78" s="14">
-        <v>78.0</v>
+        <v>79.0</v>
       </c>
       <c r="R78" s="5"/>
       <c r="S78" s="5"/>
@@ -6116,19 +6218,19 @@
     </row>
     <row r="79" ht="22.5" customHeight="1">
       <c r="A79" s="15">
-        <v>46104.60472307871</v>
+        <v>46104.62088429398</v>
       </c>
       <c r="B79" s="16" t="s">
         <v>405</v>
       </c>
       <c r="C79" s="16">
-        <v>29.0</v>
+        <v>26.0</v>
       </c>
       <c r="D79" s="16">
-        <v>9.483455859E9</v>
+        <v>9.483715512E9</v>
       </c>
       <c r="E79" s="16" t="s">
-        <v>204</v>
+        <v>42</v>
       </c>
       <c r="F79" s="16" t="s">
         <v>19</v>
@@ -6155,12 +6257,12 @@
         <v>408</v>
       </c>
       <c r="N79" s="16">
-        <v>6.08206770571E11</v>
+        <v>6.44825062844E11</v>
       </c>
       <c r="O79" s="18"/>
       <c r="P79" s="18"/>
       <c r="Q79" s="14">
-        <v>79.0</v>
+        <v>80.0</v>
       </c>
       <c r="R79" s="5"/>
       <c r="S79" s="5"/>
@@ -6169,37 +6271,37 @@
     </row>
     <row r="80" ht="22.5" customHeight="1">
       <c r="A80" s="15">
-        <v>46104.62088429398</v>
+        <v>46104.62125190972</v>
       </c>
       <c r="B80" s="16" t="s">
         <v>409</v>
       </c>
       <c r="C80" s="16">
-        <v>26.0</v>
+        <v>28.0</v>
       </c>
       <c r="D80" s="16">
-        <v>9.483715512E9</v>
+        <v>9.483495691E9</v>
       </c>
       <c r="E80" s="16" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="F80" s="16" t="s">
-        <v>19</v>
+        <v>260</v>
       </c>
       <c r="G80" s="16" t="s">
         <v>20</v>
       </c>
       <c r="H80" s="16" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="I80" s="16" t="s">
         <v>410</v>
       </c>
       <c r="J80" s="16">
-        <v>16.0</v>
+        <v>1.0</v>
       </c>
       <c r="K80" s="16" t="s">
-        <v>32</v>
+        <v>127</v>
       </c>
       <c r="L80" s="17" t="s">
         <v>411</v>
@@ -6208,12 +6310,12 @@
         <v>412</v>
       </c>
       <c r="N80" s="16">
-        <v>6.44825062844E11</v>
+        <v>6.08218631752E11</v>
       </c>
       <c r="O80" s="18"/>
       <c r="P80" s="18"/>
       <c r="Q80" s="14">
-        <v>80.0</v>
+        <v>81.0</v>
       </c>
       <c r="R80" s="5"/>
       <c r="S80" s="5"/>
@@ -6222,37 +6324,37 @@
     </row>
     <row r="81" ht="22.5" customHeight="1">
       <c r="A81" s="15">
-        <v>46104.62125190972</v>
+        <v>46104.693587013884</v>
       </c>
       <c r="B81" s="16" t="s">
         <v>413</v>
       </c>
       <c r="C81" s="16">
-        <v>28.0</v>
+        <v>32.0</v>
       </c>
       <c r="D81" s="16">
-        <v>9.483495691E9</v>
+        <v>9.480556099E9</v>
       </c>
       <c r="E81" s="16" t="s">
-        <v>55</v>
+        <v>200</v>
       </c>
       <c r="F81" s="16" t="s">
-        <v>264</v>
+        <v>19</v>
       </c>
       <c r="G81" s="16" t="s">
         <v>20</v>
       </c>
       <c r="H81" s="16" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="I81" s="16" t="s">
         <v>414</v>
       </c>
       <c r="J81" s="16">
-        <v>1.0</v>
+        <v>18.0</v>
       </c>
       <c r="K81" s="16" t="s">
-        <v>131</v>
+        <v>23</v>
       </c>
       <c r="L81" s="17" t="s">
         <v>415</v>
@@ -6261,12 +6363,12 @@
         <v>416</v>
       </c>
       <c r="N81" s="16">
-        <v>6.08218631752E11</v>
+        <v>6.08206770574E11</v>
       </c>
       <c r="O81" s="18"/>
       <c r="P81" s="18"/>
       <c r="Q81" s="14">
-        <v>81.0</v>
+        <v>82.0</v>
       </c>
       <c r="R81" s="5"/>
       <c r="S81" s="5"/>
@@ -6275,50 +6377,52 @@
     </row>
     <row r="82" ht="22.5" customHeight="1">
       <c r="A82" s="15">
-        <v>46104.693587013884</v>
+        <v>46104.699961481485</v>
       </c>
       <c r="B82" s="16" t="s">
         <v>417</v>
       </c>
       <c r="C82" s="16">
-        <v>32.0</v>
-      </c>
-      <c r="D82" s="16">
-        <v>9.480556099E9</v>
+        <v>36.0</v>
+      </c>
+      <c r="D82" s="16" t="s">
+        <v>418</v>
       </c>
       <c r="E82" s="16" t="s">
-        <v>204</v>
+        <v>36</v>
       </c>
       <c r="F82" s="16" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="G82" s="16" t="s">
         <v>20</v>
       </c>
       <c r="H82" s="16" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="I82" s="16" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="J82" s="16">
-        <v>18.0</v>
+        <v>7.0</v>
       </c>
       <c r="K82" s="16" t="s">
-        <v>23</v>
+        <v>127</v>
       </c>
       <c r="L82" s="17" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M82" s="17" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N82" s="16">
-        <v>6.08206770574E11</v>
+        <v>6.08206770573E11</v>
       </c>
       <c r="O82" s="18"/>
       <c r="P82" s="18"/>
-      <c r="Q82" s="18"/>
+      <c r="Q82" s="14">
+        <v>83.0</v>
+      </c>
       <c r="R82" s="5"/>
       <c r="S82" s="5"/>
       <c r="T82" s="5"/>
@@ -6326,19 +6430,19 @@
     </row>
     <row r="83" ht="22.5" customHeight="1">
       <c r="A83" s="15">
-        <v>46104.699961481485</v>
+        <v>46104.747592604166</v>
       </c>
       <c r="B83" s="16" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C83" s="16">
-        <v>36.0</v>
-      </c>
-      <c r="D83" s="16" t="s">
-        <v>422</v>
+        <v>26.0</v>
+      </c>
+      <c r="D83" s="16">
+        <v>9.483490361E9</v>
       </c>
       <c r="E83" s="16" t="s">
-        <v>36</v>
+        <v>18</v>
       </c>
       <c r="F83" s="16" t="s">
         <v>43</v>
@@ -6350,26 +6454,28 @@
         <v>37</v>
       </c>
       <c r="I83" s="16" t="s">
+        <v>422</v>
+      </c>
+      <c r="J83" s="16">
+        <v>99.0</v>
+      </c>
+      <c r="K83" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="L83" s="17" t="s">
         <v>423</v>
       </c>
-      <c r="J83" s="16">
-        <v>7.0</v>
-      </c>
-      <c r="K83" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="L83" s="17" t="s">
+      <c r="M83" s="17" t="s">
         <v>424</v>
       </c>
-      <c r="M83" s="17" t="s">
+      <c r="N83" s="16" t="s">
         <v>425</v>
-      </c>
-      <c r="N83" s="16">
-        <v>6.08206770573E11</v>
       </c>
       <c r="O83" s="18"/>
       <c r="P83" s="18"/>
-      <c r="Q83" s="18"/>
+      <c r="Q83" s="14">
+        <v>84.0</v>
+      </c>
       <c r="R83" s="5"/>
       <c r="S83" s="5"/>
       <c r="T83" s="5"/>
@@ -6377,16 +6483,16 @@
     </row>
     <row r="84" ht="22.5" customHeight="1">
       <c r="A84" s="15">
-        <v>46104.747592604166</v>
+        <v>46104.76058050926</v>
       </c>
       <c r="B84" s="16" t="s">
         <v>426</v>
       </c>
       <c r="C84" s="16">
-        <v>26.0</v>
+        <v>22.0</v>
       </c>
       <c r="D84" s="16">
-        <v>9.483490361E9</v>
+        <v>7.841054265E9</v>
       </c>
       <c r="E84" s="16" t="s">
         <v>18</v>
@@ -6401,26 +6507,28 @@
         <v>37</v>
       </c>
       <c r="I84" s="16" t="s">
-        <v>426</v>
-      </c>
-      <c r="J84" s="16">
-        <v>99.0</v>
+        <v>427</v>
+      </c>
+      <c r="J84" s="19" t="s">
+        <v>73</v>
       </c>
       <c r="K84" s="16" t="s">
-        <v>32</v>
+        <v>172</v>
       </c>
       <c r="L84" s="17" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M84" s="17" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N84" s="16" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O84" s="18"/>
       <c r="P84" s="18"/>
-      <c r="Q84" s="18"/>
+      <c r="Q84" s="14">
+        <v>85.0</v>
+      </c>
       <c r="R84" s="5"/>
       <c r="S84" s="5"/>
       <c r="T84" s="5"/>
@@ -6428,19 +6536,19 @@
     </row>
     <row r="85" ht="22.5" customHeight="1">
       <c r="A85" s="15">
-        <v>46104.76058050926</v>
+        <v>46104.827948969905</v>
       </c>
       <c r="B85" s="16" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C85" s="16">
-        <v>22.0</v>
+        <v>41.0</v>
       </c>
       <c r="D85" s="16">
-        <v>7.841054265E9</v>
+        <v>9.481110163E9</v>
       </c>
       <c r="E85" s="16" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F85" s="16" t="s">
         <v>43</v>
@@ -6452,26 +6560,28 @@
         <v>37</v>
       </c>
       <c r="I85" s="16" t="s">
-        <v>431</v>
-      </c>
-      <c r="J85" s="19" t="s">
-        <v>73</v>
+        <v>432</v>
+      </c>
+      <c r="J85" s="16" t="s">
+        <v>433</v>
       </c>
       <c r="K85" s="16" t="s">
-        <v>176</v>
+        <v>57</v>
       </c>
       <c r="L85" s="17" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="M85" s="17" t="s">
-        <v>433</v>
-      </c>
-      <c r="N85" s="16" t="s">
-        <v>434</v>
+        <v>435</v>
+      </c>
+      <c r="N85" s="19" t="s">
+        <v>436</v>
       </c>
       <c r="O85" s="18"/>
       <c r="P85" s="18"/>
-      <c r="Q85" s="18"/>
+      <c r="Q85" s="14">
+        <v>86.0</v>
+      </c>
       <c r="R85" s="5"/>
       <c r="S85" s="5"/>
       <c r="T85" s="5"/>
@@ -6479,22 +6589,22 @@
     </row>
     <row r="86" ht="22.5" customHeight="1">
       <c r="A86" s="15">
-        <v>46104.827948969905</v>
+        <v>46104.84469378472</v>
       </c>
       <c r="B86" s="16" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C86" s="16">
-        <v>41.0</v>
+        <v>39.0</v>
       </c>
       <c r="D86" s="16">
-        <v>9.481110163E9</v>
+        <v>9.483296756E9</v>
       </c>
       <c r="E86" s="16" t="s">
-        <v>36</v>
+        <v>83</v>
       </c>
       <c r="F86" s="16" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="G86" s="16" t="s">
         <v>20</v>
@@ -6503,26 +6613,28 @@
         <v>37</v>
       </c>
       <c r="I86" s="16" t="s">
-        <v>436</v>
-      </c>
-      <c r="J86" s="16" t="s">
-        <v>437</v>
+        <v>438</v>
+      </c>
+      <c r="J86" s="19" t="s">
+        <v>151</v>
       </c>
       <c r="K86" s="16" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="L86" s="17" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M86" s="17" t="s">
-        <v>439</v>
-      </c>
-      <c r="N86" s="19" t="s">
         <v>440</v>
+      </c>
+      <c r="N86" s="16">
+        <v>6.08206770571E11</v>
       </c>
       <c r="O86" s="18"/>
       <c r="P86" s="18"/>
-      <c r="Q86" s="18"/>
+      <c r="Q86" s="14">
+        <v>87.0</v>
+      </c>
       <c r="R86" s="5"/>
       <c r="S86" s="5"/>
       <c r="T86" s="5"/>
@@ -6530,37 +6642,37 @@
     </row>
     <row r="87" ht="22.5" customHeight="1">
       <c r="A87" s="15">
-        <v>46104.84469378472</v>
+        <v>46104.86174061343</v>
       </c>
       <c r="B87" s="16" t="s">
         <v>441</v>
       </c>
       <c r="C87" s="16">
-        <v>39.0</v>
+        <v>23.0</v>
       </c>
       <c r="D87" s="16">
-        <v>9.483296756E9</v>
+        <v>9.480044015E9</v>
       </c>
       <c r="E87" s="16" t="s">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="F87" s="16" t="s">
-        <v>88</v>
+        <v>19</v>
       </c>
       <c r="G87" s="16" t="s">
         <v>20</v>
       </c>
       <c r="H87" s="16" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="I87" s="16" t="s">
         <v>442</v>
       </c>
-      <c r="J87" s="19" t="s">
-        <v>155</v>
+      <c r="J87" s="16">
+        <v>24.0</v>
       </c>
       <c r="K87" s="16" t="s">
-        <v>131</v>
+        <v>57</v>
       </c>
       <c r="L87" s="17" t="s">
         <v>443</v>
@@ -6568,12 +6680,14 @@
       <c r="M87" s="17" t="s">
         <v>444</v>
       </c>
-      <c r="N87" s="16">
-        <v>6.08206770571E11</v>
+      <c r="N87" s="16" t="s">
+        <v>445</v>
       </c>
       <c r="O87" s="18"/>
       <c r="P87" s="18"/>
-      <c r="Q87" s="18"/>
+      <c r="Q87" s="14">
+        <v>88.0</v>
+      </c>
       <c r="R87" s="5"/>
       <c r="S87" s="5"/>
       <c r="T87" s="5"/>
@@ -6581,50 +6695,52 @@
     </row>
     <row r="88" ht="22.5" customHeight="1">
       <c r="A88" s="15">
-        <v>46104.86174061343</v>
+        <v>46105.7816933912</v>
       </c>
       <c r="B88" s="16" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C88" s="16">
-        <v>23.0</v>
+        <v>45.0</v>
       </c>
       <c r="D88" s="16">
-        <v>9.480044015E9</v>
+        <v>9.481110162E9</v>
       </c>
       <c r="E88" s="16" t="s">
         <v>36</v>
       </c>
       <c r="F88" s="16" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="G88" s="16" t="s">
         <v>20</v>
       </c>
       <c r="H88" s="16" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="I88" s="16" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="J88" s="16">
-        <v>24.0</v>
+        <v>1.0</v>
       </c>
       <c r="K88" s="16" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="L88" s="17" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="M88" s="17" t="s">
-        <v>448</v>
-      </c>
-      <c r="N88" s="16" t="s">
         <v>449</v>
+      </c>
+      <c r="N88" s="16">
+        <v>6.08206770572E11</v>
       </c>
       <c r="O88" s="18"/>
       <c r="P88" s="18"/>
-      <c r="Q88" s="18"/>
+      <c r="Q88" s="14">
+        <v>89.0</v>
+      </c>
       <c r="R88" s="5"/>
       <c r="S88" s="5"/>
       <c r="T88" s="5"/>
@@ -6632,37 +6748,37 @@
     </row>
     <row r="89" ht="22.5" customHeight="1">
       <c r="A89" s="15">
-        <v>46105.7816933912</v>
+        <v>46105.836277372684</v>
       </c>
       <c r="B89" s="16" t="s">
         <v>450</v>
       </c>
       <c r="C89" s="16">
-        <v>45.0</v>
+        <v>25.0</v>
       </c>
       <c r="D89" s="16">
-        <v>9.481110162E9</v>
+        <v>6.361845375E9</v>
       </c>
       <c r="E89" s="16" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="F89" s="16" t="s">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="G89" s="16" t="s">
         <v>20</v>
       </c>
       <c r="H89" s="16" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="I89" s="16" t="s">
         <v>451</v>
       </c>
-      <c r="J89" s="16">
-        <v>1.0</v>
+      <c r="J89" s="19" t="s">
+        <v>86</v>
       </c>
       <c r="K89" s="16" t="s">
-        <v>131</v>
+        <v>57</v>
       </c>
       <c r="L89" s="17" t="s">
         <v>452</v>
@@ -6670,12 +6786,14 @@
       <c r="M89" s="17" t="s">
         <v>453</v>
       </c>
-      <c r="N89" s="16">
-        <v>6.08206770572E11</v>
+      <c r="N89" s="16" t="s">
+        <v>454</v>
       </c>
       <c r="O89" s="18"/>
       <c r="P89" s="18"/>
-      <c r="Q89" s="18"/>
+      <c r="Q89" s="14">
+        <v>90.0</v>
+      </c>
       <c r="R89" s="5"/>
       <c r="S89" s="5"/>
       <c r="T89" s="5"/>
@@ -6683,303 +6801,510 @@
     </row>
     <row r="90" ht="22.5" customHeight="1">
       <c r="A90" s="15">
-        <v>46105.836277372684</v>
+        <v>46105.86005472222</v>
       </c>
       <c r="B90" s="16" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C90" s="16">
-        <v>25.0</v>
+        <v>42.0</v>
       </c>
       <c r="D90" s="16">
-        <v>6.361845375E9</v>
+        <v>9.48169047E9</v>
       </c>
       <c r="E90" s="16" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="F90" s="16" t="s">
-        <v>19</v>
+        <v>84</v>
       </c>
       <c r="G90" s="16" t="s">
-        <v>20</v>
+        <v>323</v>
       </c>
       <c r="H90" s="16" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="I90" s="16" t="s">
-        <v>455</v>
-      </c>
-      <c r="J90" s="19" t="s">
-        <v>90</v>
+        <v>456</v>
+      </c>
+      <c r="J90" s="16">
+        <v>18.0</v>
       </c>
       <c r="K90" s="16" t="s">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="L90" s="17" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M90" s="17" t="s">
-        <v>457</v>
-      </c>
-      <c r="N90" s="16" t="s">
         <v>458</v>
+      </c>
+      <c r="N90" s="16">
+        <v>6.08347880904E11</v>
       </c>
       <c r="O90" s="18"/>
       <c r="P90" s="18"/>
-      <c r="Q90" s="18"/>
+      <c r="Q90" s="14">
+        <v>91.0</v>
+      </c>
       <c r="R90" s="5"/>
       <c r="S90" s="5"/>
       <c r="T90" s="5"/>
       <c r="U90" s="5"/>
     </row>
     <row r="91" ht="22.5" customHeight="1">
-      <c r="A91" s="20">
-        <v>46105.86005472222</v>
-      </c>
-      <c r="B91" s="21" t="s">
+      <c r="A91" s="15">
+        <v>46106.62220894676</v>
+      </c>
+      <c r="B91" s="16" t="s">
         <v>459</v>
       </c>
-      <c r="C91" s="21">
-        <v>42.0</v>
-      </c>
-      <c r="D91" s="21">
-        <v>9.48169047E9</v>
-      </c>
-      <c r="E91" s="21" t="s">
+      <c r="C91" s="16">
+        <v>35.0</v>
+      </c>
+      <c r="D91" s="16">
+        <v>9.44967171E9</v>
+      </c>
+      <c r="E91" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="F91" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="G91" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H91" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="I91" s="16" t="s">
+        <v>460</v>
+      </c>
+      <c r="J91" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="K91" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="L91" s="17" t="s">
+        <v>461</v>
+      </c>
+      <c r="M91" s="17" t="s">
+        <v>462</v>
+      </c>
+      <c r="N91" s="16" t="s">
+        <v>463</v>
+      </c>
+      <c r="O91" s="18"/>
+      <c r="P91" s="18"/>
+      <c r="Q91" s="14">
+        <v>92.0</v>
+      </c>
+      <c r="R91" s="5"/>
+      <c r="S91" s="5"/>
+      <c r="T91" s="5"/>
+      <c r="U91" s="5"/>
+    </row>
+    <row r="92" ht="22.5" customHeight="1">
+      <c r="A92" s="15">
+        <v>46108.70305098379</v>
+      </c>
+      <c r="B92" s="16" t="s">
+        <v>464</v>
+      </c>
+      <c r="C92" s="16">
+        <v>26.0</v>
+      </c>
+      <c r="D92" s="16">
+        <v>6.36009769E8</v>
+      </c>
+      <c r="E92" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="F92" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G92" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H92" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="I92" s="16" t="s">
+        <v>465</v>
+      </c>
+      <c r="J92" s="16">
+        <v>45.0</v>
+      </c>
+      <c r="K92" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="L92" s="17" t="s">
+        <v>466</v>
+      </c>
+      <c r="M92" s="17" t="s">
+        <v>467</v>
+      </c>
+      <c r="N92" s="16" t="s">
+        <v>468</v>
+      </c>
+      <c r="O92" s="18"/>
+      <c r="P92" s="18"/>
+      <c r="Q92" s="18"/>
+      <c r="R92" s="5"/>
+      <c r="S92" s="5"/>
+      <c r="T92" s="5"/>
+      <c r="U92" s="5"/>
+    </row>
+    <row r="93" ht="22.5" customHeight="1">
+      <c r="A93" s="15">
+        <v>46111.69438103009</v>
+      </c>
+      <c r="B93" s="16" t="s">
+        <v>469</v>
+      </c>
+      <c r="C93" s="16">
+        <v>43.0</v>
+      </c>
+      <c r="D93" s="16">
+        <v>9.482602961E9</v>
+      </c>
+      <c r="E93" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="F91" s="21" t="s">
-        <v>88</v>
-      </c>
-      <c r="G91" s="21" t="s">
-        <v>327</v>
-      </c>
-      <c r="H91" s="21" t="s">
+      <c r="F93" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="G93" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H93" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="I91" s="21" t="s">
-        <v>460</v>
-      </c>
-      <c r="J91" s="21">
-        <v>18.0</v>
-      </c>
-      <c r="K91" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="L91" s="22" t="s">
-        <v>461</v>
-      </c>
-      <c r="M91" s="22" t="s">
-        <v>462</v>
-      </c>
-      <c r="N91" s="21">
-        <v>6.08347880904E11</v>
-      </c>
-    </row>
-    <row r="92" ht="22.5" customHeight="1">
-      <c r="A92" s="20">
-        <v>46106.62220894676</v>
-      </c>
-      <c r="B92" s="21" t="s">
-        <v>463</v>
-      </c>
-      <c r="C92" s="21">
-        <v>35.0</v>
-      </c>
-      <c r="D92" s="21">
-        <v>9.44967171E9</v>
-      </c>
-      <c r="E92" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="F92" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="G92" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="H92" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="I92" s="21" t="s">
-        <v>464</v>
-      </c>
-      <c r="J92" s="23" t="s">
-        <v>155</v>
-      </c>
-      <c r="K92" s="21" t="s">
-        <v>131</v>
-      </c>
-      <c r="L92" s="22" t="s">
-        <v>465</v>
-      </c>
-      <c r="M92" s="22" t="s">
-        <v>466</v>
-      </c>
-      <c r="N92" s="21" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="5"/>
-      <c r="B93" s="24"/>
-      <c r="C93" s="5"/>
-      <c r="D93" s="5"/>
-      <c r="E93" s="5"/>
-      <c r="F93" s="5"/>
-      <c r="G93" s="5"/>
-      <c r="H93" s="5"/>
-      <c r="I93" s="5"/>
-      <c r="J93" s="5"/>
-      <c r="K93" s="5"/>
-      <c r="L93" s="5"/>
-      <c r="M93" s="5"/>
-      <c r="N93" s="5"/>
-      <c r="O93" s="5"/>
-      <c r="P93" s="5"/>
-      <c r="Q93" s="5"/>
+      <c r="I93" s="16" t="s">
+        <v>470</v>
+      </c>
+      <c r="J93" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="K93" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="L93" s="17" t="s">
+        <v>471</v>
+      </c>
+      <c r="M93" s="17" t="s">
+        <v>472</v>
+      </c>
+      <c r="N93" s="16" t="s">
+        <v>473</v>
+      </c>
+      <c r="O93" s="18"/>
+      <c r="P93" s="18"/>
+      <c r="Q93" s="18"/>
       <c r="R93" s="5"/>
       <c r="S93" s="5"/>
       <c r="T93" s="5"/>
       <c r="U93" s="5"/>
     </row>
-    <row r="94">
-      <c r="A94" s="5"/>
-      <c r="B94" s="24"/>
-      <c r="C94" s="5"/>
-      <c r="D94" s="5"/>
-      <c r="E94" s="5"/>
-      <c r="F94" s="5"/>
-      <c r="G94" s="5"/>
-      <c r="H94" s="5"/>
-      <c r="I94" s="5"/>
-      <c r="J94" s="5"/>
-      <c r="K94" s="5"/>
-      <c r="L94" s="5"/>
-      <c r="M94" s="5"/>
-      <c r="N94" s="5"/>
-      <c r="O94" s="5"/>
-      <c r="P94" s="5"/>
-      <c r="Q94" s="5"/>
+    <row r="94" ht="22.5" customHeight="1">
+      <c r="A94" s="15">
+        <v>46111.70048150463</v>
+      </c>
+      <c r="B94" s="16" t="s">
+        <v>474</v>
+      </c>
+      <c r="C94" s="16">
+        <v>25.0</v>
+      </c>
+      <c r="D94" s="16">
+        <v>9.380521827E9</v>
+      </c>
+      <c r="E94" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="F94" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G94" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H94" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I94" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="J94" s="16">
+        <v>32.0</v>
+      </c>
+      <c r="K94" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L94" s="17" t="s">
+        <v>475</v>
+      </c>
+      <c r="M94" s="17" t="s">
+        <v>476</v>
+      </c>
+      <c r="N94" s="16" t="s">
+        <v>477</v>
+      </c>
+      <c r="O94" s="18"/>
+      <c r="P94" s="18"/>
+      <c r="Q94" s="18"/>
       <c r="R94" s="5"/>
       <c r="S94" s="5"/>
       <c r="T94" s="5"/>
       <c r="U94" s="5"/>
     </row>
-    <row r="95">
-      <c r="A95" s="5"/>
-      <c r="B95" s="24"/>
-      <c r="C95" s="5"/>
-      <c r="D95" s="5"/>
-      <c r="E95" s="5"/>
-      <c r="F95" s="5"/>
-      <c r="G95" s="5"/>
-      <c r="H95" s="5"/>
-      <c r="I95" s="5"/>
-      <c r="J95" s="5"/>
-      <c r="K95" s="5"/>
-      <c r="L95" s="5"/>
-      <c r="M95" s="5"/>
-      <c r="N95" s="5"/>
-      <c r="O95" s="5"/>
-      <c r="P95" s="5"/>
-      <c r="Q95" s="5"/>
+    <row r="95" ht="22.5" customHeight="1">
+      <c r="A95" s="15">
+        <v>46111.837318969905</v>
+      </c>
+      <c r="B95" s="16" t="s">
+        <v>478</v>
+      </c>
+      <c r="C95" s="16">
+        <v>15.0</v>
+      </c>
+      <c r="D95" s="16">
+        <v>9.449335679E9</v>
+      </c>
+      <c r="E95" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="F95" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="G95" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H95" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="I95" s="16" t="s">
+        <v>479</v>
+      </c>
+      <c r="J95" s="16">
+        <v>1827.0</v>
+      </c>
+      <c r="K95" s="16" t="s">
+        <v>172</v>
+      </c>
+      <c r="L95" s="17" t="s">
+        <v>480</v>
+      </c>
+      <c r="M95" s="17" t="s">
+        <v>481</v>
+      </c>
+      <c r="N95" s="16" t="s">
+        <v>482</v>
+      </c>
+      <c r="O95" s="18"/>
+      <c r="P95" s="18"/>
+      <c r="Q95" s="18"/>
       <c r="R95" s="5"/>
       <c r="S95" s="5"/>
       <c r="T95" s="5"/>
       <c r="U95" s="5"/>
     </row>
-    <row r="96">
-      <c r="A96" s="5"/>
-      <c r="B96" s="24"/>
-      <c r="C96" s="5"/>
-      <c r="D96" s="5"/>
-      <c r="E96" s="5"/>
-      <c r="F96" s="5"/>
-      <c r="G96" s="5"/>
-      <c r="H96" s="5"/>
-      <c r="I96" s="5"/>
-      <c r="J96" s="5"/>
-      <c r="K96" s="5"/>
-      <c r="L96" s="5"/>
-      <c r="M96" s="5"/>
-      <c r="N96" s="5"/>
-      <c r="O96" s="5"/>
-      <c r="P96" s="5"/>
-      <c r="Q96" s="5"/>
+    <row r="96" ht="22.5" customHeight="1">
+      <c r="A96" s="15">
+        <v>46111.86003340277</v>
+      </c>
+      <c r="B96" s="16" t="s">
+        <v>483</v>
+      </c>
+      <c r="C96" s="16">
+        <v>34.0</v>
+      </c>
+      <c r="D96" s="16">
+        <v>9.44966053E9</v>
+      </c>
+      <c r="E96" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="F96" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="G96" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H96" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="I96" s="16" t="s">
+        <v>484</v>
+      </c>
+      <c r="J96" s="16">
+        <v>24.0</v>
+      </c>
+      <c r="K96" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L96" s="17" t="s">
+        <v>485</v>
+      </c>
+      <c r="M96" s="17" t="s">
+        <v>486</v>
+      </c>
+      <c r="N96" s="16" t="s">
+        <v>487</v>
+      </c>
+      <c r="O96" s="18"/>
+      <c r="P96" s="18"/>
+      <c r="Q96" s="18"/>
       <c r="R96" s="5"/>
       <c r="S96" s="5"/>
       <c r="T96" s="5"/>
       <c r="U96" s="5"/>
     </row>
-    <row r="97">
-      <c r="A97" s="5"/>
-      <c r="B97" s="24"/>
-      <c r="C97" s="5"/>
-      <c r="D97" s="5"/>
-      <c r="E97" s="5"/>
-      <c r="F97" s="5"/>
-      <c r="G97" s="5"/>
-      <c r="H97" s="5"/>
-      <c r="I97" s="5"/>
-      <c r="J97" s="5"/>
-      <c r="K97" s="5"/>
-      <c r="L97" s="5"/>
-      <c r="M97" s="5"/>
-      <c r="N97" s="5"/>
-      <c r="O97" s="5"/>
-      <c r="P97" s="5"/>
-      <c r="Q97" s="5"/>
+    <row r="97" ht="22.5" customHeight="1">
+      <c r="A97" s="15">
+        <v>46111.86736701389</v>
+      </c>
+      <c r="B97" s="16" t="s">
+        <v>488</v>
+      </c>
+      <c r="C97" s="16">
+        <v>29.0</v>
+      </c>
+      <c r="D97" s="16">
+        <v>8.277910208E9</v>
+      </c>
+      <c r="E97" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="F97" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G97" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H97" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I97" s="16" t="s">
+        <v>489</v>
+      </c>
+      <c r="J97" s="16">
+        <v>14.0</v>
+      </c>
+      <c r="K97" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="L97" s="17" t="s">
+        <v>490</v>
+      </c>
+      <c r="M97" s="17" t="s">
+        <v>491</v>
+      </c>
+      <c r="N97" s="16" t="s">
+        <v>492</v>
+      </c>
+      <c r="O97" s="18"/>
+      <c r="P97" s="18"/>
+      <c r="Q97" s="18"/>
       <c r="R97" s="5"/>
       <c r="S97" s="5"/>
       <c r="T97" s="5"/>
       <c r="U97" s="5"/>
     </row>
-    <row r="98">
-      <c r="A98" s="5"/>
-      <c r="B98" s="24"/>
-      <c r="C98" s="5"/>
-      <c r="D98" s="5"/>
-      <c r="E98" s="5"/>
-      <c r="F98" s="5"/>
-      <c r="G98" s="5"/>
-      <c r="H98" s="5"/>
-      <c r="I98" s="5"/>
-      <c r="J98" s="5"/>
-      <c r="K98" s="5"/>
-      <c r="L98" s="5"/>
-      <c r="M98" s="5"/>
-      <c r="N98" s="5"/>
-      <c r="O98" s="5"/>
-      <c r="P98" s="5"/>
-      <c r="Q98" s="5"/>
+    <row r="98" ht="22.5" customHeight="1">
+      <c r="A98" s="15">
+        <v>46111.87122255787</v>
+      </c>
+      <c r="B98" s="16" t="s">
+        <v>493</v>
+      </c>
+      <c r="C98" s="16">
+        <v>34.0</v>
+      </c>
+      <c r="D98" s="16">
+        <v>9.480261991E9</v>
+      </c>
+      <c r="E98" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="F98" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="G98" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H98" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="I98" s="16" t="s">
+        <v>494</v>
+      </c>
+      <c r="J98" s="16">
+        <v>91.0</v>
+      </c>
+      <c r="K98" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L98" s="17" t="s">
+        <v>495</v>
+      </c>
+      <c r="M98" s="17" t="s">
+        <v>496</v>
+      </c>
+      <c r="N98" s="16">
+        <v>1.20823294729E11</v>
+      </c>
+      <c r="O98" s="18"/>
+      <c r="P98" s="18"/>
+      <c r="Q98" s="18"/>
       <c r="R98" s="5"/>
       <c r="S98" s="5"/>
       <c r="T98" s="5"/>
       <c r="U98" s="5"/>
     </row>
-    <row r="99">
-      <c r="A99" s="5"/>
-      <c r="B99" s="24"/>
-      <c r="C99" s="5"/>
-      <c r="D99" s="5"/>
-      <c r="E99" s="5"/>
-      <c r="F99" s="5"/>
-      <c r="G99" s="5"/>
-      <c r="H99" s="5"/>
-      <c r="I99" s="5"/>
-      <c r="J99" s="5"/>
-      <c r="K99" s="5"/>
-      <c r="L99" s="5"/>
-      <c r="M99" s="5"/>
-      <c r="N99" s="5"/>
-      <c r="O99" s="5"/>
-      <c r="P99" s="5"/>
-      <c r="Q99" s="5"/>
-      <c r="R99" s="5"/>
-      <c r="S99" s="5"/>
-      <c r="T99" s="5"/>
-      <c r="U99" s="5"/>
+    <row r="99" ht="22.5" customHeight="1">
+      <c r="A99" s="20">
+        <v>46112.00143276621</v>
+      </c>
+      <c r="B99" s="21" t="s">
+        <v>497</v>
+      </c>
+      <c r="C99" s="21">
+        <v>45.0</v>
+      </c>
+      <c r="D99" s="21">
+        <v>9.482906635E9</v>
+      </c>
+      <c r="E99" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="F99" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="G99" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="H99" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="I99" s="21" t="s">
+        <v>498</v>
+      </c>
+      <c r="J99" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="K99" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="L99" s="23" t="s">
+        <v>499</v>
+      </c>
+      <c r="M99" s="23" t="s">
+        <v>500</v>
+      </c>
+      <c r="N99" s="21">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="5"/>
@@ -9119,6 +9444,167 @@
       <c r="S192" s="5"/>
       <c r="T192" s="5"/>
       <c r="U192" s="5"/>
+    </row>
+    <row r="193">
+      <c r="A193" s="5"/>
+      <c r="B193" s="24"/>
+      <c r="C193" s="5"/>
+      <c r="D193" s="5"/>
+      <c r="E193" s="5"/>
+      <c r="F193" s="5"/>
+      <c r="G193" s="5"/>
+      <c r="H193" s="5"/>
+      <c r="I193" s="5"/>
+      <c r="J193" s="5"/>
+      <c r="K193" s="5"/>
+      <c r="L193" s="5"/>
+      <c r="M193" s="5"/>
+      <c r="N193" s="5"/>
+      <c r="O193" s="5"/>
+      <c r="P193" s="5"/>
+      <c r="Q193" s="5"/>
+      <c r="R193" s="5"/>
+      <c r="S193" s="5"/>
+      <c r="T193" s="5"/>
+      <c r="U193" s="5"/>
+    </row>
+    <row r="194">
+      <c r="A194" s="5"/>
+      <c r="B194" s="24"/>
+      <c r="C194" s="5"/>
+      <c r="D194" s="5"/>
+      <c r="E194" s="5"/>
+      <c r="F194" s="5"/>
+      <c r="G194" s="5"/>
+      <c r="H194" s="5"/>
+      <c r="I194" s="5"/>
+      <c r="J194" s="5"/>
+      <c r="K194" s="5"/>
+      <c r="L194" s="5"/>
+      <c r="M194" s="5"/>
+      <c r="N194" s="5"/>
+      <c r="O194" s="5"/>
+      <c r="P194" s="5"/>
+      <c r="Q194" s="5"/>
+      <c r="R194" s="5"/>
+      <c r="S194" s="5"/>
+      <c r="T194" s="5"/>
+      <c r="U194" s="5"/>
+    </row>
+    <row r="195">
+      <c r="A195" s="5"/>
+      <c r="B195" s="24"/>
+      <c r="C195" s="5"/>
+      <c r="D195" s="5"/>
+      <c r="E195" s="5"/>
+      <c r="F195" s="5"/>
+      <c r="G195" s="5"/>
+      <c r="H195" s="5"/>
+      <c r="I195" s="5"/>
+      <c r="J195" s="5"/>
+      <c r="K195" s="5"/>
+      <c r="L195" s="5"/>
+      <c r="M195" s="5"/>
+      <c r="N195" s="5"/>
+      <c r="O195" s="5"/>
+      <c r="P195" s="5"/>
+      <c r="Q195" s="5"/>
+      <c r="R195" s="5"/>
+      <c r="S195" s="5"/>
+      <c r="T195" s="5"/>
+      <c r="U195" s="5"/>
+    </row>
+    <row r="196">
+      <c r="A196" s="5"/>
+      <c r="B196" s="24"/>
+      <c r="C196" s="5"/>
+      <c r="D196" s="5"/>
+      <c r="E196" s="5"/>
+      <c r="F196" s="5"/>
+      <c r="G196" s="5"/>
+      <c r="H196" s="5"/>
+      <c r="I196" s="5"/>
+      <c r="J196" s="5"/>
+      <c r="K196" s="5"/>
+      <c r="L196" s="5"/>
+      <c r="M196" s="5"/>
+      <c r="N196" s="5"/>
+      <c r="O196" s="5"/>
+      <c r="P196" s="5"/>
+      <c r="Q196" s="5"/>
+      <c r="R196" s="5"/>
+      <c r="S196" s="5"/>
+      <c r="T196" s="5"/>
+      <c r="U196" s="5"/>
+    </row>
+    <row r="197">
+      <c r="A197" s="5"/>
+      <c r="B197" s="24"/>
+      <c r="C197" s="5"/>
+      <c r="D197" s="5"/>
+      <c r="E197" s="5"/>
+      <c r="F197" s="5"/>
+      <c r="G197" s="5"/>
+      <c r="H197" s="5"/>
+      <c r="I197" s="5"/>
+      <c r="J197" s="5"/>
+      <c r="K197" s="5"/>
+      <c r="L197" s="5"/>
+      <c r="M197" s="5"/>
+      <c r="N197" s="5"/>
+      <c r="O197" s="5"/>
+      <c r="P197" s="5"/>
+      <c r="Q197" s="5"/>
+      <c r="R197" s="5"/>
+      <c r="S197" s="5"/>
+      <c r="T197" s="5"/>
+      <c r="U197" s="5"/>
+    </row>
+    <row r="198">
+      <c r="A198" s="5"/>
+      <c r="B198" s="24"/>
+      <c r="C198" s="5"/>
+      <c r="D198" s="5"/>
+      <c r="E198" s="5"/>
+      <c r="F198" s="5"/>
+      <c r="G198" s="5"/>
+      <c r="H198" s="5"/>
+      <c r="I198" s="5"/>
+      <c r="J198" s="5"/>
+      <c r="K198" s="5"/>
+      <c r="L198" s="5"/>
+      <c r="M198" s="5"/>
+      <c r="N198" s="5"/>
+      <c r="O198" s="5"/>
+      <c r="P198" s="5"/>
+      <c r="Q198" s="5"/>
+      <c r="R198" s="5"/>
+      <c r="S198" s="5"/>
+      <c r="T198" s="5"/>
+      <c r="U198" s="5"/>
+    </row>
+    <row r="199">
+      <c r="A199" s="5"/>
+      <c r="B199" s="24"/>
+      <c r="C199" s="5"/>
+      <c r="D199" s="5"/>
+      <c r="E199" s="5"/>
+      <c r="F199" s="5"/>
+      <c r="G199" s="5"/>
+      <c r="H199" s="5"/>
+      <c r="I199" s="5"/>
+      <c r="J199" s="5"/>
+      <c r="K199" s="5"/>
+      <c r="L199" s="5"/>
+      <c r="M199" s="5"/>
+      <c r="N199" s="5"/>
+      <c r="O199" s="5"/>
+      <c r="P199" s="5"/>
+      <c r="Q199" s="5"/>
+      <c r="R199" s="5"/>
+      <c r="S199" s="5"/>
+      <c r="T199" s="5"/>
+      <c r="U199" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -9304,11 +9790,25 @@
     <hyperlink r:id="rId181" ref="M91"/>
     <hyperlink r:id="rId182" ref="L92"/>
     <hyperlink r:id="rId183" ref="M92"/>
+    <hyperlink r:id="rId184" ref="L93"/>
+    <hyperlink r:id="rId185" ref="M93"/>
+    <hyperlink r:id="rId186" ref="L94"/>
+    <hyperlink r:id="rId187" ref="M94"/>
+    <hyperlink r:id="rId188" ref="L95"/>
+    <hyperlink r:id="rId189" ref="M95"/>
+    <hyperlink r:id="rId190" ref="L96"/>
+    <hyperlink r:id="rId191" ref="M96"/>
+    <hyperlink r:id="rId192" ref="L97"/>
+    <hyperlink r:id="rId193" ref="M97"/>
+    <hyperlink r:id="rId194" ref="L98"/>
+    <hyperlink r:id="rId195" ref="M98"/>
+    <hyperlink r:id="rId196" ref="L99"/>
+    <hyperlink r:id="rId197" ref="M99"/>
   </hyperlinks>
-  <drawing r:id="rId184"/>
-  <legacyDrawing r:id="rId185"/>
+  <drawing r:id="rId198"/>
+  <legacyDrawing r:id="rId199"/>
   <tableParts count="1">
-    <tablePart r:id="rId187"/>
+    <tablePart r:id="rId201"/>
   </tableParts>
 </worksheet>
 </file>
